--- a/산출물/기능명세서.xlsx
+++ b/산출물/기능명세서.xlsx
@@ -4,7 +4,7 @@
   <sheets>
     <sheet name="기능명세" sheetId="1" r:id="rId1"/>
     <sheet name="요약" sheetId="2" r:id="rId2"/>
-    <sheet name="분석기라우팅" sheetId="3" r:id="rId3"/>
+    <sheet name="분석기선택규칙" sheetId="3" r:id="rId3"/>
     <sheet name="비기능·제외" sheetId="4" r:id="rId4"/>
     <sheet name="미결사항" sheetId="5" r:id="rId5"/>
   </sheets>
@@ -879,7 +879,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">C. 문서 입력·처리   (15건 · P0 10 · P1 3)</t>
+          <t xml:space="preserve">C. 문서 입력·처리   (16건 · P0 10 · P1 4)</t>
         </is>
       </c>
       <c r="B20" s="3"/>
@@ -1528,68 +1528,72 @@
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>
     </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DOC-16</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C. 문서 입력·처리</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업로드 시 문서 유형 지정 (기본값 자동 판별)</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">재정</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DOC-01</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유형을 고르면 분류 분석기를 건너뛴다. 자동 판별을 고르면 분류 분석기가 먼저 실행되고 결과가 확정값으로 저장된다</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">일괄은 배치 단위로 한 번 지정. ANL-04 의 전제</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">D. OCR 검수   (18건 · P0 0 · P1 10)</t>
         </is>
       </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REV-01</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">D. OCR 검수</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">페이지 이미지 생성 · 저장</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">재정</t>
-        </is>
-      </c>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">페이지별 이미지와 좌표 기준 크기(width·height)가 저장된다</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">document_pages</t>
-        </is>
-      </c>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">REV-02</t>
+          <t xml:space="preserve">REV-01</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -1599,7 +1603,7 @@
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">OCR 박스 저장</t>
+          <t xml:space="preserve">페이지 이미지 생성 · 저장</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -1617,26 +1621,22 @@
           <t xml:space="preserve">재정</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REV-01</t>
-        </is>
-      </c>
+      <c r="G38" s="4"/>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">박스별 텍스트·좌표·신뢰도가 0~1 비율 좌표로 저장된다</t>
+          <t xml:space="preserve">페이지별 이미지와 좌표 기준 크기(width·height)가 저장된다</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ocr_elements</t>
+          <t xml:space="preserve">document_pages</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">REV-03</t>
+          <t xml:space="preserve">REV-02</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">이미지 위 Bounding Box 표시</t>
+          <t xml:space="preserve">OCR 박스 저장</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -1666,24 +1666,24 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">REV-02</t>
+          <t xml:space="preserve">REV-01</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">화면 확대·축소와 무관하게 박스가 글자 위에 정확히 얹힌다</t>
+          <t xml:space="preserve">박스별 텍스트·좌표·신뢰도가 0~1 비율 좌표로 저장된다</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">좌표 기준 이미지 고정 필요</t>
+          <t xml:space="preserve">ocr_elements</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">REV-04</t>
+          <t xml:space="preserve">REV-03</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">신뢰도별 박스 구분</t>
+          <t xml:space="preserve">이미지 위 Bounding Box 표시</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -1713,20 +1713,24 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">REV-03</t>
+          <t xml:space="preserve">REV-02</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">높음·검토권장·낮음·선택 네 가지가 시각적으로 구분된다</t>
-        </is>
-      </c>
-      <c r="I40" s="4"/>
+          <t xml:space="preserve">화면 확대·축소와 무관하게 박스가 글자 위에 정확히 얹힌다</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">좌표 기준 이미지 고정 필요</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">REV-05</t>
+          <t xml:space="preserve">REV-04</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -1736,7 +1740,7 @@
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">박스 선택 + 텍스트 수정</t>
+          <t xml:space="preserve">신뢰도별 박스 구분</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -1761,7 +1765,7 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">수정 후 original_text 는 그대로 남고 text 만 바뀐다</t>
+          <t xml:space="preserve">높음·검토권장·낮음·선택 네 가지가 시각적으로 구분된다</t>
         </is>
       </c>
       <c r="I41" s="4"/>
@@ -1769,7 +1773,7 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">REV-06</t>
+          <t xml:space="preserve">REV-05</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -1779,7 +1783,7 @@
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">낮은 신뢰도만 모아보기</t>
+          <t xml:space="preserve">박스 선택 + 텍스트 수정</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -1799,12 +1803,12 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">REV-04</t>
+          <t xml:space="preserve">REV-03</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">임계치 미만 박스만 목록으로 순회할 수 있다</t>
+          <t xml:space="preserve">수정 후 original_text 는 그대로 남고 text 만 바뀐다</t>
         </is>
       </c>
       <c r="I42" s="4"/>
@@ -1812,93 +1816,93 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">REV-06</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D. OCR 검수</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">낮은 신뢰도만 모아보기</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">재정</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REV-04</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">임계치 미만 박스만 목록으로 순회할 수 있다</t>
+        </is>
+      </c>
+      <c r="I43" s="4"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">REV-07</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">D. OCR 검수</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">검수 완료 처리</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">재정</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">REV-05</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">완료 시 is_confirmed=true, 확정자·시각이 남고 분석이 1회 실행된다</t>
         </is>
       </c>
-      <c r="I43" s="4"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REV-08</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">D. OCR 검수</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">박스 이동 · 크기 조정</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E44" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F44" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">재정</t>
-        </is>
-      </c>
-      <c r="G44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REV-05</t>
-        </is>
-      </c>
-      <c r="H44" s="8"/>
-      <c r="I44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">크기만 바꾸면 텍스트 유지</t>
-        </is>
-      </c>
+      <c r="I44" s="4"/>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">REV-09</t>
+          <t xml:space="preserve">REV-08</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -1908,7 +1912,7 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">박스 생성 · 삭제</t>
+          <t xml:space="preserve">박스 이동 · 크기 조정</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
@@ -1934,14 +1938,14 @@
       <c r="H45" s="8"/>
       <c r="I45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">삭제는 논리 삭제</t>
+          <t xml:space="preserve">크기만 바꾸면 텍스트 유지</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">REV-10</t>
+          <t xml:space="preserve">REV-09</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
@@ -1951,7 +1955,7 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">박스 병합 · 분리</t>
+          <t xml:space="preserve">박스 생성 · 삭제</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
@@ -1971,16 +1975,20 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">REV-08</t>
+          <t xml:space="preserve">REV-05</t>
         </is>
       </c>
       <c r="H46" s="8"/>
-      <c r="I46" s="8"/>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">삭제는 논리 삭제</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">REV-11</t>
+          <t xml:space="preserve">REV-10</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -1990,7 +1998,7 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">선택 영역 다시 OCR</t>
+          <t xml:space="preserve">박스 병합 · 분리</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
@@ -2014,16 +2022,12 @@
         </is>
       </c>
       <c r="H47" s="8"/>
-      <c r="I47" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사용자 확인 후 반영. source=RE_OCR</t>
-        </is>
-      </c>
+      <c r="I47" s="8"/>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">REV-12</t>
+          <t xml:space="preserve">REV-11</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
@@ -2033,7 +2037,7 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">단락 지정 · 병합 · 분리</t>
+          <t xml:space="preserve">선택 영역 다시 OCR</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
@@ -2053,20 +2057,20 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">REV-02</t>
+          <t xml:space="preserve">REV-08</t>
         </is>
       </c>
       <c r="H48" s="8"/>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">OCR 재실행 불필요</t>
+          <t xml:space="preserve">사용자 확인 후 반영. source=RE_OCR</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">REV-13</t>
+          <t xml:space="preserve">REV-12</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -2076,7 +2080,7 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">읽기 순서 변경</t>
+          <t xml:space="preserve">단락 지정 · 병합 · 분리</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
@@ -2096,24 +2100,20 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">REV-12</t>
-        </is>
-      </c>
-      <c r="H49" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사용자 지정이 자동 결과를 덮지 않는다</t>
-        </is>
-      </c>
+          <t xml:space="preserve">REV-02</t>
+        </is>
+      </c>
+      <c r="H49" s="8"/>
       <c r="I49" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">지정 순서 &gt; 지정 단락 &gt; XY-Cut</t>
+          <t xml:space="preserve">OCR 재실행 불필요</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">REV-14</t>
+          <t xml:space="preserve">REV-13</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">표 행 · 열 수동 보정</t>
+          <t xml:space="preserve">읽기 순서 변경</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
@@ -2146,103 +2146,103 @@
           <t xml:space="preserve">REV-12</t>
         </is>
       </c>
-      <c r="H50" s="8"/>
-      <c r="I50" s="8"/>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용자 지정이 자동 결과를 덮지 않는다</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지정 순서 &gt; 지정 단락 &gt; XY-Cut</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">REV-14</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D. OCR 검수</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">표 행 · 열 수동 보정</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">재정</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REV-12</t>
+        </is>
+      </c>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">REV-15</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">D. OCR 검수</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">수정 이력 · 되돌리기</t>
         </is>
       </c>
-      <c r="D51" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E51" s="10" t="inlineStr">
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="F51" s="10" t="inlineStr">
+      <c r="F52" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">재정</t>
         </is>
       </c>
-      <c r="G51" s="8" t="inlineStr">
+      <c r="G52" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">REV-05</t>
         </is>
       </c>
-      <c r="H51" s="8"/>
-      <c r="I51" s="8" t="inlineStr">
+      <c r="H52" s="8"/>
+      <c r="I52" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">ocr_element_revisions</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REV-16</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">D. OCR 검수</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동시 수정 충돌 방지</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">재정</t>
-        </is>
-      </c>
-      <c r="G52" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REV-02</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">같은 박스를 두 사용자가 수정하면 나중 요청이 409 를 받는다</t>
-        </is>
-      </c>
-      <c r="I52" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ocr_elements.version</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">REV-17</t>
+          <t xml:space="preserve">REV-16</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">텍스트 재조립</t>
+          <t xml:space="preserve">동시 수정 충돌 방지</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -2272,223 +2272,223 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">REV-05</t>
+          <t xml:space="preserve">REV-02</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">박스 수정 후 extracted_texts.content 가 같은 트랜잭션에서 갱신된다</t>
+          <t xml:space="preserve">같은 박스를 두 사용자가 수정하면 나중 요청이 409 를 받는다</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">조각 offset 도 함께 남긴다 — ANL-13</t>
+          <t xml:space="preserve">ocr_elements.version</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">REV-17</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D. OCR 검수</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">텍스트 재조립</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">재정</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REV-05</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박스 수정 후 extracted_texts.content 가 같은 트랜잭션에서 갱신된다</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">offset 기록 불필요 — ANL-13 폐기</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">REV-18</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">D. OCR 검수</t>
         </is>
       </c>
-      <c r="C54" s="9" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">분석 결과 오래됨 표시</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">재정</t>
         </is>
       </c>
-      <c r="G54" s="4" t="inlineStr">
+      <c r="G55" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">REV-17</t>
         </is>
       </c>
-      <c r="H54" s="4" t="inlineStr">
+      <c r="H55" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">OCR 을 고친 뒤 화면에 '분석을 다시 실행해 주세요' 가 뜬다</t>
         </is>
       </c>
-      <c r="I54" s="4" t="inlineStr">
+      <c r="I55" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">revision 전파 사슬</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">E. 일괄 처리   (7건 · P0 0 · P1 2)</t>
         </is>
       </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BAT-01</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">E. 일괄 처리</t>
-        </is>
-      </c>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다중 파일 순차 업로드</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">재정</t>
-        </is>
-      </c>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DOC-01</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">여러 파일을 한 번에 등록하고 파일별로 성공·실패가 표시된다</t>
-        </is>
-      </c>
-      <c r="I56" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">브라우저 순차 호출로 충분</t>
-        </is>
-      </c>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">BAT-01</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E. 일괄 처리</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다중 파일 순차 업로드</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">재정</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DOC-01</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">여러 파일을 한 번에 등록하고 파일별로 성공·실패가 표시된다</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">브라우저 순차 호출로 충분</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">BAT-02</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">E. 일괄 처리</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C58" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">처리 대기열 화면</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">재정</t>
         </is>
       </c>
-      <c r="G57" s="4" t="inlineStr">
+      <c r="G58" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">BAT-01</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr">
+      <c r="H58" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">대기·처리중·검수필요·완료·실패가 파일별로 보이고 실패 사유가 표시된다</t>
         </is>
       </c>
-      <c r="I57" s="4"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BAT-03</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">E. 일괄 처리</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서버 일괄 작업 모델</t>
-        </is>
-      </c>
-      <c r="D58" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E58" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F58" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">재정</t>
-        </is>
-      </c>
-      <c r="G58" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DOC-06</t>
-        </is>
-      </c>
-      <c r="H58" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">브라우저를 닫아도 작업이 계속된다</t>
-        </is>
-      </c>
-      <c r="I58" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">batch_jobs / batch_items</t>
-        </is>
-      </c>
+      <c r="I58" s="4"/>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">BAT-04</t>
+          <t xml:space="preserve">BAT-03</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">실패 재시도</t>
+          <t xml:space="preserve">서버 일괄 작업 모델</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
@@ -2518,16 +2518,24 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">BAT-03</t>
-        </is>
-      </c>
-      <c r="H59" s="8"/>
-      <c r="I59" s="8"/>
+          <t xml:space="preserve">DOC-06</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">브라우저를 닫아도 작업이 계속된다</t>
+        </is>
+      </c>
+      <c r="I59" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">batch_jobs / batch_items</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">BAT-05</t>
+          <t xml:space="preserve">BAT-04</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
@@ -2537,7 +2545,7 @@
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">OCR Worker 수 제한 병렬</t>
+          <t xml:space="preserve">실패 재시도</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
@@ -2561,16 +2569,12 @@
         </is>
       </c>
       <c r="H60" s="8"/>
-      <c r="I60" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">메모리 한도 안에서</t>
-        </is>
-      </c>
+      <c r="I60" s="8"/>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">BAT-06</t>
+          <t xml:space="preserve">BAT-05</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -2580,7 +2584,7 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">실시간 진행률 (SSE)</t>
+          <t xml:space="preserve">OCR Worker 수 제한 병렬</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
@@ -2604,105 +2608,109 @@
         </is>
       </c>
       <c r="H61" s="8"/>
-      <c r="I61" s="8"/>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">메모리 한도 안에서</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">BAT-06</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E. 일괄 처리</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">실시간 진행률 (SSE)</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F62" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">재정</t>
+        </is>
+      </c>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAT-03</t>
+        </is>
+      </c>
+      <c r="H62" s="8"/>
+      <c r="I62" s="8"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">BAT-07</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">E. 일괄 처리</t>
         </is>
       </c>
-      <c r="C62" s="8" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">로컬 폴더 자동 감시 프로그램</t>
         </is>
       </c>
-      <c r="D62" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E62" s="10" t="inlineStr">
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">P3</t>
         </is>
       </c>
-      <c r="F62" s="10" t="inlineStr">
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">재정</t>
         </is>
       </c>
-      <c r="G62" s="8"/>
-      <c r="H62" s="8"/>
-      <c r="I62" s="8" t="inlineStr">
+      <c r="G63" s="8"/>
+      <c r="H63" s="8"/>
+      <c r="I63" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">별도 설치형. 범위 밖</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F. 분석   (13건 · P0 4 · P1 5)</t>
-        </is>
-      </c>
-      <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
-      <c r="G63" s="3"/>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANL-01</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F. 분석</t>
-        </is>
-      </c>
-      <c r="C64" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요약 분석기</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기존</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P0</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">보현</t>
-        </is>
-      </c>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요약문과 토큰·지연시간이 기록된다</t>
-        </is>
-      </c>
-      <c r="I64" s="4"/>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F. 분석   (12건 · P0 4 · P1 4)</t>
+        </is>
+      </c>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+      <c r="H64" s="3"/>
+      <c r="I64" s="3"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-02</t>
+          <t xml:space="preserve">ANL-01</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -2712,7 +2720,7 @@
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">분류 분석기</t>
+          <t xml:space="preserve">요약 분석기</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -2733,19 +2741,15 @@
       <c r="G65" s="4"/>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">6종 카테고리 중 하나로 분류된다</t>
-        </is>
-      </c>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">라우팅의 선행 고정 단계</t>
-        </is>
-      </c>
+          <t xml:space="preserve">요약문과 토큰·지연시간이 기록된다</t>
+        </is>
+      </c>
+      <c r="I65" s="4"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-03</t>
+          <t xml:space="preserve">ANL-02</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -2755,17 +2759,17 @@
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">액션아이템 분석기</t>
+          <t xml:space="preserve">분류 분석기</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규</t>
+          <t xml:space="preserve">확장</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
@@ -2775,71 +2779,71 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-13</t>
+          <t xml:space="preserve">DOC-16</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">내용·담당자·기한·확신도를 배열로 반환. 담당자·기한을 못 찾으면 미지정 표시</t>
+          <t xml:space="preserve">자동 판별을 고른 문서에만 실행된다. 7종 중 하나로 분류하고 reason 을 함께 반환한다</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">제안 골격의 첫 사례</t>
+          <t xml:space="preserve">사람이 유형을 고르면 건너뛴다</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">ANL-03</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F. 분석</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">액션아이템 분석기</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">ANL-04</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F. 분석</t>
-        </is>
-      </c>
-      <c r="C67" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">분석기 라우팅</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">보현</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANL-02</t>
-        </is>
-      </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">문서 유형에 따라 실행할 분석기가 결정된다. 새 분석기 추가 시 라우팅 표에 행 하나 추가로 끝난다</t>
+          <t xml:space="preserve">내용·담당자·기한·확신도·reason(왜 이걸 뽑았는지)을 배열로 반환. 담당자·기한을 못 찾으면 미지정 표시</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">analyzer_routes 테이블</t>
+          <t xml:space="preserve">제안 골격의 첫 사례</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-05</t>
+          <t xml:space="preserve">ANL-04</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -2849,7 +2853,7 @@
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석 진행률 일반화</t>
+          <t xml:space="preserve">분석기 선택 규칙</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -2869,24 +2873,24 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-04</t>
+          <t xml:space="preserve">DOC-16</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">진행 단계가 분석기 수에 따라 자동으로 '분석 2/3' 처럼 표시된다. 분석기 추가 시 화면 코드를 고치지 않는다</t>
+          <t xml:space="preserve">문서 유형에 따라 실행할 분석기가 결정된다. 새 분석기 추가 시 규칙 표에 행 하나 추가로 끝난다</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">목업 4단계 하드코딩 해소</t>
+          <t xml:space="preserve">analyzer_rules 테이블. FastAPI 라우터와 무관</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-06</t>
+          <t xml:space="preserve">ANL-05</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -2896,7 +2900,7 @@
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">확정 텍스트 기준 분석</t>
+          <t xml:space="preserve">분석 진행률 일반화</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -2916,20 +2920,24 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">REV-07</t>
+          <t xml:space="preserve">ANL-04</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">검수 완료된 문서는 수정된 텍스트로 분석된다. 어느 ocr_revision 을 썼는지 기록된다</t>
-        </is>
-      </c>
-      <c r="I69" s="4"/>
+          <t xml:space="preserve">진행 단계가 분석기 수에 따라 자동으로 '분석 2/3' 처럼 표시된다. 분석기 추가 시 화면 코드를 고치지 않는다</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목업 4단계 하드코딩 해소</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-07</t>
+          <t xml:space="preserve">ANL-06</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -2939,17 +2947,17 @@
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석 이력 보존</t>
+          <t xml:space="preserve">확정 텍스트 기준 분석</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">기존</t>
+          <t xml:space="preserve">신규</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
@@ -2957,22 +2965,22 @@
           <t xml:space="preserve">보현</t>
         </is>
       </c>
-      <c r="G70" s="4"/>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REV-07</t>
+        </is>
+      </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">재분석이 이전 결과를 덮지 않는다</t>
-        </is>
-      </c>
-      <c r="I70" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">analyses 1:N</t>
-        </is>
-      </c>
+          <t xml:space="preserve">검수 완료된 문서는 수정된 텍스트로 분석된다. 어느 ocr_revision 을 썼는지 기록된다</t>
+        </is>
+      </c>
+      <c r="I70" s="4"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-08</t>
+          <t xml:space="preserve">ANL-07</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -2982,7 +2990,7 @@
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">프롬프트 버전 관리</t>
+          <t xml:space="preserve">분석 이력 보존</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -3003,58 +3011,58 @@
       <c r="G71" s="4"/>
       <c r="H71" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">재분석이 이전 결과를 덮지 않는다</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">analyses 1:N</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-08</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F. 분석</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프롬프트 버전 관리</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기존</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">prompt_version 이 결과와 함께 저장된다</t>
         </is>
       </c>
-      <c r="I71" s="4"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANL-09</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F. 분석</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LLM 재시도 · 폴백</t>
-        </is>
-      </c>
-      <c r="D72" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E72" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F72" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">보현</t>
-        </is>
-      </c>
-      <c r="G72" s="8"/>
-      <c r="H72" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일시 실패 시 재시도, 지속 실패 시 대체 모델</t>
-        </is>
-      </c>
-      <c r="I72" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">현재 타임아웃만 있다</t>
-        </is>
-      </c>
+      <c r="I72" s="4"/>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-10</t>
+          <t xml:space="preserve">ANL-09</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
@@ -3064,7 +3072,7 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석기별 채택률 지표</t>
+          <t xml:space="preserve">LLM 재시도 · 폴백</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
@@ -3082,26 +3090,22 @@
           <t xml:space="preserve">보현</t>
         </is>
       </c>
-      <c r="G73" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TSK-07</t>
-        </is>
-      </c>
+      <c r="G73" s="8"/>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">채택률이 분석기별로 나뉘어 표시된다</t>
+          <t xml:space="preserve">일시 실패 시 재시도, 지속 실패 시 대체 모델</t>
         </is>
       </c>
       <c r="I73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">목업은 단일 숫자</t>
+          <t xml:space="preserve">현재 타임아웃만 있다</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-11</t>
+          <t xml:space="preserve">ANL-10</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
@@ -3111,7 +3115,7 @@
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">교정 분석기</t>
+          <t xml:space="preserve">분석기별 채택률 지표</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
@@ -3121,7 +3125,7 @@
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -3131,16 +3135,24 @@
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-04</t>
-        </is>
-      </c>
-      <c r="H74" s="8"/>
-      <c r="I74" s="8"/>
+          <t xml:space="preserve">TSK-07</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">채택률이 분석기별로 나뉘어 표시된다</t>
+        </is>
+      </c>
+      <c r="I74" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목업은 단일 숫자</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-12</t>
+          <t xml:space="preserve">ANL-11</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
@@ -3150,7 +3162,7 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">번역 분석기</t>
+          <t xml:space="preserve">교정 분석기</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
@@ -3177,51 +3189,43 @@
       <c r="I75" s="8"/>
     </row>
     <row r="76">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANL-13</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-12</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">F. 분석</t>
         </is>
       </c>
-      <c r="C76" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Analyzer Protocol 확장 — 위치 컨텍스트</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="inlineStr">
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">번역 분석기</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="F76" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">보현</t>
         </is>
       </c>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REV-17</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">분석기가 근거 페이지와 좌표를 결과에 담을 수 있다. 기존 두 분석기는 고치지 않는다</t>
-        </is>
-      </c>
-      <c r="I76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">없으면 TSK-04·AMT-09 역추적 불가. 규격을 첫 주에 확정</t>
-        </is>
-      </c>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-04</t>
+        </is>
+      </c>
+      <c r="H76" s="8"/>
+      <c r="I76" s="8"/>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="3" t="inlineStr">
@@ -3271,12 +3275,12 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-13</t>
+          <t xml:space="preserve">ANL-04</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">항목명·수량·단위·단가·금액·근거 페이지와 원문 인용을 구조화 스키마로 반환. 스키마에 없는 필드는 나올 수 없다</t>
+          <t xml:space="preserve">항목명·수량·단위·단가·금액·reason(왜 이 항목으로 봤는지)을 구조화 스키마로 반환. 스키마에 없는 필드는 나올 수 없다</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
@@ -3615,7 +3619,7 @@
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">금액 근거 역추적</t>
+          <t xml:space="preserve">금액 판단 근거 표시</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -3635,17 +3639,17 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-13</t>
+          <t xml:space="preserve">AMT-01</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">금액 숫자를 누르면 문서 원문의 해당 위치가 하이라이트된다</t>
+          <t xml:space="preserve">금액 항목마다 reason 이 보이고 출처 문서로 이동할 수 있다</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ocr_element_id 사용</t>
+          <t xml:space="preserve">위치 하이라이트는 범위 밖. 검증은 AMT-03</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3900,7 @@
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">근거 역추적</t>
+          <t xml:space="preserve">출처 · 판단 근거 표시</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
@@ -3916,17 +3920,17 @@
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-13</t>
+          <t xml:space="preserve">TSK-03</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">태스크에서 출처를 누르면 문서 원문의 해당 문단이 하이라이트된다. 페이지 번호가 함께 표시된다</t>
+          <t xml:space="preserve">태스크에 출처 문서 링크와 AI 판단 근거(reason)가 함께 보인다. 링크를 누르면 문서 상세로 이동한다</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-13 없이는 불가</t>
+          <t xml:space="preserve">원문 위치 하이라이트는 범위 밖</t>
         </is>
       </c>
     </row>
@@ -5029,10 +5033,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">구현 20일 (8/17~9/5 · 영업일 15일 · 3인 45 인일). P0+P1 을 다 못 하므로 '묶기' 로 접근한다.</t>
+          <t xml:space="preserve">구현 20일 (8/17~9/5 · 영업일 15일 · 3인 45 인일). P0+P1 을 다 못 하므로 '묶기' 로 접근한다. 근거 페이지 표시를 범위에서 빼면서 ANL-13(분석기 규격 확장)이 폐기되어 세 사람의 인터페이스 대기가 하나 줄었다.</t>
         </is>
       </c>
     </row>
@@ -5135,13 +5139,13 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="5">
         <v>10</v>
       </c>
       <c r="D7" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" s="5">
         <v>1</v>
@@ -5216,13 +5220,13 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="5">
         <v>4</v>
       </c>
       <c r="D10" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10" s="5">
         <v>2</v>
@@ -5487,25 +5491,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석기 라우팅 (ANL-04)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="34" customHeight="1">
+          <t xml:space="preserve">분석기 선택 규칙 (ANL-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="46" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">문서 유형에 따라 실행할 분석기를 정한다. 분류(CATEGORY)는 라우팅 대상이 아니라 모든 문서에 무조건 먼저 실행되는 고정 선행 단계다 — 분류 결과가 라우팅 기준이 되므로 순환을 피해야 한다.</t>
+          <t xml:space="preserve">문서 유형에 따라 실행할 분석기를 정한다. FastAPI 라우터와는 무관한 층이다. 유형은 업로드할 때 정해진다(DOC-16) — 사람이 고르면 분류 분석기를 건너뛰고, 자동 판별을 고르면 분류만 먼저 실행해 확정값을 만든다. 이렇게 해야 '분류는 분석 결과인데 선택은 분석 전' 인 순환이 풀린다.</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5517,7 @@
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문서 유형 (document_type)</t>
+          <t xml:space="preserve">문서 유형 (document_type) — 7종</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -5545,7 +5549,7 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">회의록</t>
+          <t xml:space="preserve">계약서 CONTRACT</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -5555,29 +5559,29 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">O</t>
+          <t xml:space="preserve">자동일 때만</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">O</t>
+          <t xml:space="preserve">조항 검토</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">비용 발생 요인만</t>
+          <t xml:space="preserve">O — 계약금액</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">meeting_v1</t>
+          <t xml:space="preserve">contract_v1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약서</t>
+          <t xml:space="preserve">계약변경 CONTRACT_CHANGE</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -5587,7 +5591,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">O</t>
+          <t xml:space="preserve">자동일 때만</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -5597,19 +5601,19 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">O</t>
+          <t xml:space="preserve">O — 증감액</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">contract_v1</t>
+          <t xml:space="preserve">change_v1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">보고서</t>
+          <t xml:space="preserve">회의록 MEETING_NOTES</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -5619,29 +5623,29 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">자동일 때만</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">O</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O</t>
-        </is>
-      </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">진행률 대비</t>
+          <t xml:space="preserve">비용 발생 요인만</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">report_v1</t>
+          <t xml:space="preserve">meeting_v1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">공지사항</t>
+          <t xml:space="preserve">보고서 REPORT</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -5651,29 +5655,29 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">자동일 때만</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">O</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">진행률 대비</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">report_v1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">메뉴얼</t>
+          <t xml:space="preserve">공지사항 NOTICE</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -5683,7 +5687,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">O</t>
+          <t xml:space="preserve">자동일 때만</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -5705,7 +5709,7 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타</t>
+          <t xml:space="preserve">메뉴얼 MANUAL</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -5715,30 +5719,62 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">자동일 때만</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 ETC</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">O</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자동일 때만</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prompt_variant 가 필요한 이유 — 같은 액션아이템 분석기라도 회의록(담당자·기한 중심)과 계약서(조항 검토 중심)는 프롬프트가 달라야 한다. 목업 보드의 '하도급 계약 조항 검토' 카드가 그 사례다.</t>
+    <row r="12"/>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prompt_variant 가 필요한 이유 — 같은 분석기라도 문서 유형에 따라 프롬프트가 달라야 한다. 액션아이템은 회의록(담당자·기한 중심)과 계약서(조항 검토 중심)가 다르고, 금액은 계약서(계약금액)와 계약변경(증감액)이 다르다. 계약변경을 별도 유형으로 나눈 이유가 이것이다 — 프롬프트가 스스로 판단하게 하면 그게 또 하나의 분류 문제가 되고 틀렸을 때 사람이 고칠 방법이 없다.</t>
         </is>
       </c>
     </row>
@@ -6241,7 +6277,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">우선순위</t>
+          <t xml:space="preserve">결정됨</t>
         </is>
       </c>
       <c r="B7" s="5">
@@ -6249,12 +6285,12 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-13 Protocol 확장을 언제 하는지</t>
+          <t xml:space="preserve">근거 페이지·좌표 하이라이트 범위 제외</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">구현 첫 주에 규격만 확정. 페이크 값으로 병렬 진행</t>
+          <t xml:space="preserve">확정 — reason(판단 근거 서술)만 표시. ANL-13 폐기</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -6268,7 +6304,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">설계</t>
+          <t xml:space="preserve">결정됨</t>
         </is>
       </c>
       <c r="B8" s="5">
@@ -6276,17 +6312,17 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석기 규격에 위치 정보 추가 (ANL-13)</t>
+          <t xml:space="preserve">문서 유형을 업로드 시 지정 (기본값 자동 판별)</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">analyze(text, context=None). 기존 두 분석기는 안 고친다</t>
+          <t xml:space="preserve">확정 — DOC-16. 일괄은 배치 단위 지정</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
+          <t xml:space="preserve">전원</t>
         </is>
       </c>
       <c r="F8" s="4"/>
@@ -6322,7 +6358,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">설계</t>
+          <t xml:space="preserve">결정됨</t>
         </is>
       </c>
       <c r="B10" s="5">
@@ -6330,17 +6366,17 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">분류 결과를 라우팅 기준으로 격상 (document_type)</t>
+          <t xml:space="preserve">문서 유형을 7종으로 (계약변경 추가)</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">분류를 고정 선행 단계로. documents 컬럼 의미가 바뀐다</t>
+          <t xml:space="preserve">확정 — 원계약은 계약금액, 변경합의서는 증감액. 프롬프트가 다르다</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">전원</t>
         </is>
       </c>
       <c r="F10" s="4"/>
@@ -6362,7 +6398,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">틀리면 라우팅도 틀린다</t>
+          <t xml:space="preserve">허용. document_type_source=USER_CORRECTED 로 기록하면 분류 오류율이 나온다</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -6384,7 +6420,7 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">tasks 출처를 nullable FK 3개로 둘지</t>
+          <t xml:space="preserve">tasks 출처를 nullable FK 2개로 둘지</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -6438,7 +6474,7 @@
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">analyzer_routes 를 테이블로 둘지 코드 상수로 둘지</t>
+          <t xml:space="preserve">analyzer_rules 를 테이블로 둘지 코드 상수로 둘지</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">

--- a/산출물/기능명세서.xlsx
+++ b/산출물/기능명세서.xlsx
@@ -4,16 +4,17 @@
   <sheets>
     <sheet name="기능명세" sheetId="1" r:id="rId1"/>
     <sheet name="요약" sheetId="2" r:id="rId2"/>
-    <sheet name="분석기선택규칙" sheetId="3" r:id="rId3"/>
+    <sheet name="분석기구성" sheetId="3" r:id="rId3"/>
     <sheet name="비기능·제외" sheetId="4" r:id="rId4"/>
-    <sheet name="미결사항" sheetId="5" r:id="rId5"/>
+    <sheet name="폐기" sheetId="5" r:id="rId5"/>
+    <sheet name="미결사항" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="맑은 고딕"/>
@@ -41,6 +42,12 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
+      <color rgb="FF8C8C8C"/>
       <name val="맑은 고딕"/>
     </font>
   </fonts>
@@ -97,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -129,6 +136,12 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -148,13 +161,13 @@
     <col min="6" max="6" width="8" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="8" width="62" customWidth="1"/>
-    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="9" max="9" width="32" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">DocFlow 기능명세서 — 전체 108건</t>
+          <t xml:space="preserve">DocFlow 기능명세서 — 유효 116건 (폐기 6건은 별도 시트)</t>
         </is>
       </c>
     </row>
@@ -569,11 +582,7 @@
           <t xml:space="preserve">내가 멤버인 프로젝트만 나온다. 카드에 문서 수·열린 태스크·승인 대기 표시</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미확정 금액 지표 추가 — AMT-08</t>
-        </is>
-      </c>
+      <c r="I12" s="4"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -1100,11 +1109,7 @@
           <t xml:space="preserve">업로드 시 모드가 저장되고 기본값은 일반. 검수 모드는 review_status=PENDING 으로 시작</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">목업에 없음 — UI 변경 8</t>
-        </is>
-      </c>
+      <c r="I25" s="4"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -1363,7 +1368,7 @@
       <c r="G31" s="4"/>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">하위 데이터(추출텍스트·분석·OCR요소)가 함께 정리된다</t>
+          <t xml:space="preserve">하위 데이터(추출텍스트·분석·OCR요소·금액·결정·일정)가 함께 정리된다</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -1491,7 +1496,11 @@
           <t xml:space="preserve">컨테이너 재기동 후에도 파일이 유지된다</t>
         </is>
       </c>
-      <c r="I34" s="4"/>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">산출물 파일도 같은 곳에 둔다</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
@@ -1541,7 +1550,7 @@
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">업로드 시 문서 유형 지정 (기본값 자동 판별)</t>
+          <t xml:space="preserve">업로드 시 문서 유형 지정</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -1566,12 +1575,12 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">유형을 고르면 분류 분석기를 건너뛴다. 자동 판별을 고르면 분류 분석기가 먼저 실행되고 결과가 확정값으로 저장된다</t>
+          <t xml:space="preserve">7종 중 고르거나 자동 판별(기본값). 일괄은 배치 단위로 한 번 지정한다</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">일괄은 배치 단위로 한 번 지정. ANL-04 의 전제</t>
+          <t xml:space="preserve">분석기를 껐다 켜지는 않는다. 목록 필터·프롬프트 힌트·산출물 분류에 쓴다</t>
         </is>
       </c>
     </row>
@@ -1723,7 +1732,7 @@
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">좌표 기준 이미지 고정 필요</t>
+          <t xml:space="preserve">좌표 기준 이미지를 렌더링본으로 고정</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2338,7 @@
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">offset 기록 불필요 — ANL-13 폐기</t>
+          <t xml:space="preserve">offset 기록은 불필요 (ANL-13 폐기)</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2447,7 @@
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">브라우저 순차 호출로 충분</t>
+          <t xml:space="preserve">브라우저 순차 호출로 데모 충분</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2704,7 @@
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">F. 분석   (12건 · P0 4 · P1 4)</t>
+          <t xml:space="preserve">F. 분석   (13건 · P0 4 · P1 5)</t>
         </is>
       </c>
       <c r="B64" s="3"/>
@@ -2744,7 +2753,11 @@
           <t xml:space="preserve">요약문과 토큰·지연시간이 기록된다</t>
         </is>
       </c>
-      <c r="I65" s="4"/>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">코드를 고치지 않는다</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
@@ -2784,14 +2797,10 @@
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">자동 판별을 고른 문서에만 실행된다. 7종 중 하나로 분류하고 reason 을 함께 반환한다</t>
-        </is>
-      </c>
-      <c r="I66" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사람이 유형을 고르면 건너뛴다</t>
-        </is>
-      </c>
+          <t xml:space="preserve">7종 중 하나로 분류하고 reason 을 함께 반환한다. 자동 판별인 문서에만 실행한다</t>
+        </is>
+      </c>
+      <c r="I66" s="4"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
@@ -2806,7 +2815,7 @@
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">액션아이템 분석기</t>
+          <t xml:space="preserve">항목 추출 분석기</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -2824,14 +2833,10 @@
           <t xml:space="preserve">보현</t>
         </is>
       </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANL-04</t>
-        </is>
-      </c>
+      <c r="G67" s="4"/>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">내용·담당자·기한·확신도·reason(왜 이걸 뽑았는지)을 배열로 반환. 담당자·기한을 못 찾으면 미지정 표시</t>
+          <t xml:space="preserve">액션아이템·결정·일정을 한 번의 호출로 배열로 반환. 각 항목에 reason 과 확신도가 붙는다</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -2843,7 +2848,7 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-04</t>
+          <t xml:space="preserve">ANL-05</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -2853,7 +2858,7 @@
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석기 선택 규칙</t>
+          <t xml:space="preserve">분석 진행률 일반화</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -2871,26 +2876,22 @@
           <t xml:space="preserve">보현</t>
         </is>
       </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DOC-16</t>
-        </is>
-      </c>
+      <c r="G68" s="4"/>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">문서 유형에 따라 실행할 분석기가 결정된다. 새 분석기 추가 시 규칙 표에 행 하나 추가로 끝난다</t>
+          <t xml:space="preserve">진행 단계가 분석기 수에 따라 자동으로 '분석 3/4' 처럼 표시된다. 분석기 추가 시 화면 코드를 고치지 않는다</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">analyzer_rules 테이블. FastAPI 라우터와 무관</t>
+          <t xml:space="preserve">목업 4단계 하드코딩 해소</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-05</t>
+          <t xml:space="preserve">ANL-06</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -2900,7 +2901,7 @@
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석 진행률 일반화</t>
+          <t xml:space="preserve">확정 텍스트 기준 분석</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -2920,24 +2921,20 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-04</t>
+          <t xml:space="preserve">REV-07</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">진행 단계가 분석기 수에 따라 자동으로 '분석 2/3' 처럼 표시된다. 분석기 추가 시 화면 코드를 고치지 않는다</t>
-        </is>
-      </c>
-      <c r="I69" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">목업 4단계 하드코딩 해소</t>
-        </is>
-      </c>
+          <t xml:space="preserve">검수 완료된 문서는 수정된 텍스트로 분석된다. 어느 ocr_revision 을 썼는지 기록된다</t>
+        </is>
+      </c>
+      <c r="I69" s="4"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-06</t>
+          <t xml:space="preserve">ANL-07</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -2947,17 +2944,17 @@
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">확정 텍스트 기준 분석</t>
+          <t xml:space="preserve">분석 이력 보존</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규</t>
+          <t xml:space="preserve">기존</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
@@ -2965,22 +2962,22 @@
           <t xml:space="preserve">보현</t>
         </is>
       </c>
-      <c r="G70" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REV-07</t>
-        </is>
-      </c>
+      <c r="G70" s="4"/>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">검수 완료된 문서는 수정된 텍스트로 분석된다. 어느 ocr_revision 을 썼는지 기록된다</t>
-        </is>
-      </c>
-      <c r="I70" s="4"/>
+          <t xml:space="preserve">재분석이 이전 결과를 덮지 않는다</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">analyses 1:N</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-07</t>
+          <t xml:space="preserve">ANL-08</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -2990,7 +2987,7 @@
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석 이력 보존</t>
+          <t xml:space="preserve">프롬프트 버전 관리</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -3011,58 +3008,62 @@
       <c r="G71" s="4"/>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">재분석이 이전 결과를 덮지 않는다</t>
+          <t xml:space="preserve">prompt_version 이 결과와 함께 저장된다</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">analyses 1:N</t>
+          <t xml:space="preserve">분석기별로 따로 올린다</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANL-08</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-09</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">F. 분석</t>
         </is>
       </c>
-      <c r="C72" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프롬프트 버전 관리</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기존</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P0</t>
-        </is>
-      </c>
-      <c r="F72" s="5" t="inlineStr">
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LLM 재시도 · 폴백</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F72" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">보현</t>
         </is>
       </c>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prompt_version 이 결과와 함께 저장된다</t>
-        </is>
-      </c>
-      <c r="I72" s="4"/>
+      <c r="G72" s="8"/>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">일시 실패 시 재시도, 지속 실패 시 대체 모델</t>
+        </is>
+      </c>
+      <c r="I72" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현재 타임아웃만 있다</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-09</t>
+          <t xml:space="preserve">ANL-10</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
@@ -3072,7 +3073,7 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LLM 재시도 · 폴백</t>
+          <t xml:space="preserve">제안 종류별 채택률</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
@@ -3090,22 +3091,26 @@
           <t xml:space="preserve">보현</t>
         </is>
       </c>
-      <c r="G73" s="8"/>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSK-07</t>
+        </is>
+      </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">일시 실패 시 재시도, 지속 실패 시 대체 모델</t>
+          <t xml:space="preserve">채택률이 액션아이템·결정·일정·금액별로 나뉘어 표시된다</t>
         </is>
       </c>
       <c r="I73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">현재 타임아웃만 있다</t>
+          <t xml:space="preserve">목업은 단일 숫자</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-10</t>
+          <t xml:space="preserve">ANL-11</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
@@ -3115,7 +3120,7 @@
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석기별 채택률 지표</t>
+          <t xml:space="preserve">교정 분석기</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
@@ -3125,7 +3130,7 @@
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -3133,26 +3138,14 @@
           <t xml:space="preserve">보현</t>
         </is>
       </c>
-      <c r="G74" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TSK-07</t>
-        </is>
-      </c>
-      <c r="H74" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">채택률이 분석기별로 나뉘어 표시된다</t>
-        </is>
-      </c>
-      <c r="I74" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">목업은 단일 숫자</t>
-        </is>
-      </c>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
+      <c r="I74" s="8"/>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-11</t>
+          <t xml:space="preserve">ANL-12</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
@@ -3162,7 +3155,7 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">교정 분석기</t>
+          <t xml:space="preserve">번역 분석기</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
@@ -3180,129 +3173,133 @@
           <t xml:space="preserve">보현</t>
         </is>
       </c>
-      <c r="G75" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANL-04</t>
-        </is>
-      </c>
+      <c r="G75" s="8"/>
       <c r="H75" s="8"/>
       <c r="I75" s="8"/>
     </row>
     <row r="76">
-      <c r="A76" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANL-12</t>
-        </is>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-14</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">F. 분석</t>
         </is>
       </c>
-      <c r="C76" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">번역 분석기</t>
-        </is>
-      </c>
-      <c r="D76" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E76" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="F76" s="10" t="inlineStr">
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정사항 추출</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">보현</t>
         </is>
       </c>
-      <c r="G76" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANL-04</t>
-        </is>
-      </c>
-      <c r="H76" s="8"/>
-      <c r="I76" s="8"/>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G. 금액·비용추계   (11건 · P0 0 · P1 8)</t>
-        </is>
-      </c>
-      <c r="B77" s="3"/>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
-      <c r="G77" s="3"/>
-      <c r="H77" s="3"/>
-      <c r="I77" s="3"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AMT-01</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G. 금액·비용추계</t>
-        </is>
-      </c>
-      <c r="C78" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">금액 항목 추출</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-03</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">회의록에서 결정된 것을 뽑아 decisions 에 쌓는다. 결론이 안 난 것은 PENDING 으로 남아 회의 안건이 된다</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-05·DLV-06 의 재료</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-15</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F. 분석</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">일정 · 기한 추출</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="F78" s="5" t="inlineStr">
+      <c r="F77" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">보현</t>
         </is>
       </c>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANL-04</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">항목명·수량·단위·단가·금액·reason(왜 이 항목으로 봤는지)을 구조화 스키마로 반환. 스키마에 없는 필드는 나올 수 없다</t>
-        </is>
-      </c>
-      <c r="I78" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">문서에 없는 값은 비운다</t>
-        </is>
-      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-03</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문서의 날짜를 뽑아 schedule_items 에 쌓는다. 날짜는 형식이 있어 원문 대조로 정확도를 잴 수 있다</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-04·DLV-07 의 재료</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G. 금액   (8건 · P0 0 · P1 6)</t>
+        </is>
+      </c>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="3"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMT-02</t>
+          <t xml:space="preserve">AMT-01</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">G. 금액·비용추계</t>
+          <t xml:space="preserve">G. 금액</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">금액 항목 승인 · 수정 UI</t>
+          <t xml:space="preserve">금액 항목 추출</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -3320,36 +3317,32 @@
           <t xml:space="preserve">보현</t>
         </is>
       </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AMT-01</t>
-        </is>
-      </c>
+      <c r="G79" s="4"/>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">액션아이템과 같은 제안 카드 형식. 승인 전에는 어디에도 반영되지 않는다</t>
+          <t xml:space="preserve">항목명·수량·단위·금액·reason 을 구조화 스키마로 반환. 문서에 없는 값은 비운다</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI 패턴 재사용</t>
+          <t xml:space="preserve">LLM 은 추출만. 계산은 코드</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMT-03</t>
+          <t xml:space="preserve">AMT-02</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">G. 금액·비용추계</t>
+          <t xml:space="preserve">G. 금액</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">검증 모드 — 문서 합계와 대조</t>
+          <t xml:space="preserve">금액 항목 승인 · 수정 UI</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -3374,29 +3367,29 @@
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">항목 합계와 문서에 적힌 합계가 다르면 불일치 금액과 함께 표시된다</t>
+          <t xml:space="preserve">액션아이템과 같은 제안 카드 형식. 승인 전에는 어디에도 반영되지 않는다</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">금액만 가능한 검증</t>
+          <t xml:space="preserve">UI 패턴 재사용</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMT-04</t>
+          <t xml:space="preserve">AMT-03</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">G. 금액·비용추계</t>
+          <t xml:space="preserve">G. 금액</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">단가 마스터 관리</t>
+          <t xml:space="preserve">합계 대조</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -3414,32 +3407,36 @@
           <t xml:space="preserve">보현</t>
         </is>
       </c>
-      <c r="G81" s="4"/>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMT-01</t>
+        </is>
+      </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">단가마다 출처와 기준일이 있고 화면에 표시된다. 사람이 수정 가능</t>
+          <t xml:space="preserve">항목 합계와 문서에 적힌 합계가 다르면 불일치 금액과 함께 표시된다</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">최대 위험 — 범위 합의 필요</t>
+          <t xml:space="preserve">검증 가능한 유일한 기능</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMT-05</t>
+          <t xml:space="preserve">AMT-06</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">G. 금액·비용추계</t>
+          <t xml:space="preserve">G. 금액</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">전제 입력 · 승인</t>
+          <t xml:space="preserve">프로젝트 금액 집계</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -3459,305 +3456,301 @@
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMT-04</t>
+          <t xml:space="preserve">AMT-02</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">계산에 필요한 전제가 비어 있으면 계산을 실행하지 않고 무엇이 빈지 알려준다</t>
-        </is>
-      </c>
-      <c r="I82" s="4"/>
+          <t xml:space="preserve">여러 문서의 금액을 프로젝트 단위로 모은다. 같은 입력이면 항상 같은 결과가 나온다</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">단위테스트로 확인. 추계가 아니라 집계</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">AMT-07</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G. 금액</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">불일치 태스크 제안</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSK-03</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">불일치 시 태스크 제안 카드가 생긴다. 자동 등록은 하지 않는다</t>
+        </is>
+      </c>
+      <c r="I83" s="4"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMT-08</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G. 금액</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로젝트 금액 현황</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F84" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">AMT-06</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G. 금액·비용추계</t>
-        </is>
-      </c>
-      <c r="C83" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">추계 계산</t>
-        </is>
-      </c>
-      <c r="D83" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="inlineStr">
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">계약금액·변경 증감·집행률·잔액이 프로젝트 단위로 보인다</t>
+        </is>
+      </c>
+      <c r="I84" s="8"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMT-09</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G. 금액</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">금액 판단 근거 표시</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="F83" s="5" t="inlineStr">
+      <c r="F85" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">보현</t>
         </is>
       </c>
-      <c r="G83" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AMT-05</t>
-        </is>
-      </c>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Python 이 계산한다. 같은 입력이면 항상 같은 결과가 나온다 (단위테스트로 확인)</t>
-        </is>
-      </c>
-      <c r="I83" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LLM 은 계산하지 않는다</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AMT-07</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G. 금액·비용추계</t>
-        </is>
-      </c>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">불일치 · 미확정 태스크 제안</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E84" s="5" t="inlineStr">
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMT-01</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">금액 항목마다 reason 이 보이고 출처 문서로 이동할 수 있다</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">위치 하이라이트는 범위 밖</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMT-11</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G. 금액</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">금액 열람 권한 분리</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F86" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G86" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRJ-07</t>
+        </is>
+      </c>
+      <c r="H86" s="8"/>
+      <c r="I86" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미결 — VIEWER 노출 여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H. 태스크·협업   (10건 · P0 0 · P1 8)</t>
+        </is>
+      </c>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3"/>
+      <c r="I87" s="3"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSK-01</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H. 태스크·협업</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">태스크 CRUD</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">보현</t>
-        </is>
-      </c>
-      <c r="G84" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TSK-03</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">불일치 또는 전제 미확정 시 태스크 제안 카드가 생긴다. 자동 등록은 하지 않는다</t>
-        </is>
-      </c>
-      <c r="I84" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">보드를 채우는 소재</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AMT-08</t>
-        </is>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G. 금액·비용추계</t>
-        </is>
-      </c>
-      <c r="C85" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프로젝트 금액 현황</t>
-        </is>
-      </c>
-      <c r="D85" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E85" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F85" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">보현</t>
-        </is>
-      </c>
-      <c r="G85" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AMT-06</t>
-        </is>
-      </c>
-      <c r="H85" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">계약금액·변경 증감·미확정 금액이 프로젝트 단위로 집계된다</t>
-        </is>
-      </c>
-      <c r="I85" s="8"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AMT-09</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G. 금액·비용추계</t>
-        </is>
-      </c>
-      <c r="C86" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">금액 판단 근거 표시</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세현</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRJ-01</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제목·설명·담당자·기한·상태를 사람이 직접 만들 수 있다</t>
+        </is>
+      </c>
+      <c r="I88" s="4"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSK-02</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H. 태스크·협업</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">칸반 보드</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">보현</t>
-        </is>
-      </c>
-      <c r="G86" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AMT-01</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">금액 항목마다 reason 이 보이고 출처 문서로 이동할 수 있다</t>
-        </is>
-      </c>
-      <c r="I86" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위치 하이라이트는 범위 밖. 검증은 AMT-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AMT-10</t>
-        </is>
-      </c>
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G. 금액·비용추계</t>
-        </is>
-      </c>
-      <c r="C87" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비용추계서 서식 출력</t>
-        </is>
-      </c>
-      <c r="D87" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E87" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="F87" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">보현</t>
-        </is>
-      </c>
-      <c r="G87" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AMT-06</t>
-        </is>
-      </c>
-      <c r="H87" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">확정된 항목을 서식에 배치한다. 생성이 아니라 배치</t>
-        </is>
-      </c>
-      <c r="I87" s="8"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AMT-11</t>
-        </is>
-      </c>
-      <c r="B88" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G. 금액·비용추계</t>
-        </is>
-      </c>
-      <c r="C88" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">금액 열람 권한 분리</t>
-        </is>
-      </c>
-      <c r="D88" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E88" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F88" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">보현</t>
-        </is>
-      </c>
-      <c r="G88" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRJ-07</t>
-        </is>
-      </c>
-      <c r="H88" s="8"/>
-      <c r="I88" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미결 — VIEWER 노출 여부</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">H. 태스크·협업   (10건 · P0 0 · P1 8)</t>
-        </is>
-      </c>
-      <c r="B89" s="3"/>
-      <c r="C89" s="3"/>
-      <c r="D89" s="3"/>
-      <c r="E89" s="3"/>
-      <c r="F89" s="3"/>
-      <c r="G89" s="3"/>
-      <c r="H89" s="3"/>
-      <c r="I89" s="3"/>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세현</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSK-01</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">할 일·진행 중·완료 3열, 열별 개수 표시, 드래그로 상태 변경</t>
+        </is>
+      </c>
+      <c r="I89" s="4"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TSK-01</t>
+          <t xml:space="preserve">TSK-03</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -3767,7 +3760,7 @@
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">태스크 CRUD</t>
+          <t xml:space="preserve">AI 제안 → 태스크 확정</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -3787,20 +3780,24 @@
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRJ-01</t>
+          <t xml:space="preserve">ANL-03</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">제목·설명·담당자·기한·상태를 사람이 직접 만들 수 있다</t>
-        </is>
-      </c>
-      <c r="I90" s="4"/>
+          <t xml:space="preserve">승인해야 등록된다. 승인 전에는 보드에 나타나지 않는다</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자동 등록 금지 원칙</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TSK-02</t>
+          <t xml:space="preserve">TSK-04</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -3810,7 +3807,7 @@
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">칸반 보드</t>
+          <t xml:space="preserve">출처 · 판단 근거 표시</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -3830,67 +3827,67 @@
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TSK-01</t>
+          <t xml:space="preserve">TSK-03</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">할 일·진행 중·완료 3열, 열별 개수 표시, 드래그로 상태 변경</t>
-        </is>
-      </c>
-      <c r="I91" s="4"/>
+          <t xml:space="preserve">태스크에 출처 문서 링크와 AI 판단 근거(reason)가 함께 보인다</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원문 위치 하이라이트는 범위 밖</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">TSK-05</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H. 태스크·협업</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI 생성 배지 · 필터</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세현</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">TSK-03</t>
         </is>
       </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">H. 태스크·협업</t>
-        </is>
-      </c>
-      <c r="C92" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AI 제안 → 태스크 확정</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E92" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F92" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세현</t>
-        </is>
-      </c>
-      <c r="G92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANL-03</t>
-        </is>
-      </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">승인해야 등록된다. 승인 전에는 보드에 나타나지 않는다</t>
-        </is>
-      </c>
-      <c r="I92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">자동 등록 금지 원칙</t>
-        </is>
-      </c>
+          <t xml:space="preserve">AI 생성 태스크가 구분 표시되고 AI생성만·기한임박·출처문서별 필터가 동작한다</t>
+        </is>
+      </c>
+      <c r="I92" s="4"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TSK-04</t>
+          <t xml:space="preserve">TSK-06</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -3900,7 +3897,7 @@
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">출처 · 판단 근거 표시</t>
+          <t xml:space="preserve">담당자 · 기한 지정</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
@@ -3920,24 +3917,20 @@
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TSK-03</t>
+          <t xml:space="preserve">TSK-01</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">태스크에 출처 문서 링크와 AI 판단 근거(reason)가 함께 보인다. 링크를 누르면 문서 상세로 이동한다</t>
-        </is>
-      </c>
-      <c r="I93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">원문 위치 하이라이트는 범위 밖</t>
-        </is>
-      </c>
+          <t xml:space="preserve">AI 가 못 찾은 경우 미지정 상태로 남고 사람이 채운다</t>
+        </is>
+      </c>
+      <c r="I93" s="4"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TSK-05</t>
+          <t xml:space="preserve">TSK-07</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
@@ -3947,7 +3940,7 @@
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI 생성 배지 · 필터</t>
+          <t xml:space="preserve">제안 거부</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
@@ -3972,19 +3965,19 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI 생성 태스크가 구분 표시되고 AI생성만·기한임박·출처문서별 필터가 동작한다</t>
+          <t xml:space="preserve">거부한 제안은 다시 뜨지 않는다. 거부 사실이 기록된다</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석기별 구분 필요</t>
+          <t xml:space="preserve">채택률 지표의 원천</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TSK-06</t>
+          <t xml:space="preserve">TSK-08</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -3994,7 +3987,7 @@
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">담당자 · 기한 지정</t>
+          <t xml:space="preserve">일괄 승인</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
@@ -4014,163 +4007,127 @@
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TSK-01</t>
+          <t xml:space="preserve">TSK-03</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI 가 못 찾은 경우 미지정 상태로 남고 사람이 채운다</t>
+          <t xml:space="preserve">문서 단위로 여러 제안을 한 번에 승인할 수 있다</t>
         </is>
       </c>
       <c r="I95" s="4"/>
     </row>
     <row r="96">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TSK-07</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSK-09</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">H. 태스크·협업</t>
         </is>
       </c>
-      <c r="C96" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제안 거부</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F96" s="5" t="inlineStr">
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">활동 로그</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E96" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F96" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">세현</t>
         </is>
       </c>
-      <c r="G96" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TSK-03</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">거부한 제안은 다시 뜨지 않는다. 거부 사실이 기록된다</t>
-        </is>
-      </c>
-      <c r="I96" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">채택률 지표의 원천</t>
+      <c r="G96" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRJ-01</t>
+        </is>
+      </c>
+      <c r="H96" s="8"/>
+      <c r="I96" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">activity_logs. 주간 보고서 재료</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TSK-08</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSK-10</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">H. 태스크·협업</t>
         </is>
       </c>
-      <c r="C97" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일괄 승인</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F97" s="5" t="inlineStr">
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">알림 (이메일 · Slack)</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E97" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="F97" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">세현</t>
         </is>
       </c>
-      <c r="G97" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TSK-03</t>
-        </is>
-      </c>
-      <c r="H97" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">문서 단위로 여러 제안을 한 번에 승인할 수 있다</t>
-        </is>
-      </c>
-      <c r="I97" s="4"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="10" t="inlineStr">
+      <c r="G97" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">TSK-09</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">H. 태스크·협업</t>
-        </is>
-      </c>
-      <c r="C98" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">활동 로그</t>
-        </is>
-      </c>
-      <c r="D98" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E98" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F98" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세현</t>
-        </is>
-      </c>
-      <c r="G98" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRJ-01</t>
-        </is>
-      </c>
-      <c r="H98" s="8"/>
-      <c r="I98" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">activity_logs</t>
-        </is>
-      </c>
+      <c r="H97" s="8"/>
+      <c r="I97" s="8"/>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I. 가시성   (8건 · P0 0 · P1 1)</t>
+        </is>
+      </c>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+      <c r="I98" s="3"/>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">TSK-10</t>
+          <t xml:space="preserve">VIS-01</t>
         </is>
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">H. 태스크·협업</t>
+          <t xml:space="preserve">I. 가시성</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">알림 (이메일 · Slack)</t>
+          <t xml:space="preserve">대시보드 지표 카드</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
@@ -4180,84 +4137,116 @@
       </c>
       <c r="E99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">공통</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">TSK-09</t>
+          <t xml:space="preserve">PRJ-01</t>
         </is>
       </c>
       <c r="H99" s="8"/>
-      <c r="I99" s="8"/>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I. 가시성   (9건 · P0 0 · P1 1)</t>
-        </is>
-      </c>
-      <c r="B100" s="3"/>
-      <c r="C100" s="3"/>
-      <c r="D100" s="3"/>
-      <c r="E100" s="3"/>
-      <c r="F100" s="3"/>
-      <c r="G100" s="3"/>
-      <c r="H100" s="3"/>
-      <c r="I100" s="3"/>
+      <c r="I99" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전체 문서·처리 중·열린 태스크·승인 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIS-02</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I. 가시성</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문서 유형 분포</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E100" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F100" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공통</t>
+        </is>
+      </c>
+      <c r="G100" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-02</t>
+        </is>
+      </c>
+      <c r="H100" s="8"/>
+      <c r="I100" s="8"/>
     </row>
     <row r="101">
-      <c r="A101" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VIS-01</t>
-        </is>
-      </c>
-      <c r="B101" s="8" t="inlineStr">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIS-03</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">I. 가시성</t>
         </is>
       </c>
-      <c r="C101" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대시보드 지표 카드</t>
-        </is>
-      </c>
-      <c r="D101" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E101" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F101" s="10" t="inlineStr">
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">승인 대기 배너</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">공통</t>
         </is>
       </c>
-      <c r="G101" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRJ-01</t>
-        </is>
-      </c>
-      <c r="H101" s="8"/>
-      <c r="I101" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전체 문서·처리 중·열린 태스크·승인 대기</t>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSK-03</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">승인 대기 건수와 출처 문서명이 보이고 검토 화면으로 이동한다</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제안 종류별로 나눠 표시</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIS-02</t>
+          <t xml:space="preserve">VIS-04</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
@@ -4267,7 +4256,7 @@
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">문서 유형 분포</t>
+          <t xml:space="preserve">최근 문서</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
@@ -4287,67 +4276,59 @@
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-02</t>
+          <t xml:space="preserve">DOC-08</t>
         </is>
       </c>
       <c r="H102" s="8"/>
-      <c r="I102" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">유형별 분석기 목록 함께 표시</t>
-        </is>
-      </c>
+      <c r="I102" s="8"/>
     </row>
     <row r="103">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VIS-03</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIS-05</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">I. 가시성</t>
         </is>
       </c>
-      <c r="C103" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">승인 대기 배너</t>
-        </is>
-      </c>
-      <c r="D103" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E103" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F103" s="5" t="inlineStr">
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이번 주 활동</t>
+        </is>
+      </c>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E103" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F103" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">공통</t>
         </is>
       </c>
-      <c r="G103" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TSK-03</t>
-        </is>
-      </c>
-      <c r="H103" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">승인 대기 건수와 출처 문서명이 보이고 검토 화면으로 이동한다</t>
-        </is>
-      </c>
-      <c r="I103" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">분석기별로 나눠 표시</t>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-10</t>
+        </is>
+      </c>
+      <c r="H103" s="8"/>
+      <c r="I103" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제안 종류별 채택률 포함</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIS-04</t>
+          <t xml:space="preserve">VIS-06</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
@@ -4357,7 +4338,7 @@
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">최근 문서</t>
+          <t xml:space="preserve">통합 검색 (PostgreSQL FTS)</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
@@ -4377,16 +4358,20 @@
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOC-08</t>
+          <t xml:space="preserve">PRJ-08</t>
         </is>
       </c>
       <c r="H104" s="8"/>
-      <c r="I104" s="8"/>
+      <c r="I104" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로젝트 스코프 안에서</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIS-05</t>
+          <t xml:space="preserve">VIS-07</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
@@ -4396,7 +4381,7 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">이번 주 활동</t>
+          <t xml:space="preserve">시맨틱 검색 (pgvector)</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
@@ -4406,7 +4391,7 @@
       </c>
       <c r="E105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr">
@@ -4416,20 +4401,16 @@
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-10</t>
+          <t xml:space="preserve">VIS-06</t>
         </is>
       </c>
       <c r="H105" s="8"/>
-      <c r="I105" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">분석기별 채택률 포함</t>
-        </is>
-      </c>
+      <c r="I105" s="8"/>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIS-06</t>
+          <t xml:space="preserve">VIS-09</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
@@ -4439,7 +4420,7 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">통합 검색 (PostgreSQL FTS)</t>
+          <t xml:space="preserve">활동 타임라인</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
@@ -4459,152 +4440,152 @@
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRJ-08</t>
+          <t xml:space="preserve">TSK-09</t>
         </is>
       </c>
       <c r="H106" s="8"/>
-      <c r="I106" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프로젝트 스코프 안에서</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VIS-07</t>
-        </is>
-      </c>
-      <c r="B107" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I. 가시성</t>
-        </is>
-      </c>
-      <c r="C107" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">시맨틱 검색 (pgvector)</t>
-        </is>
-      </c>
-      <c r="D107" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E107" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="F107" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">공통</t>
-        </is>
-      </c>
-      <c r="G107" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VIS-06</t>
-        </is>
-      </c>
-      <c r="H107" s="8"/>
-      <c r="I107" s="8"/>
+      <c r="I106" s="8"/>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">J. 공통·기반   (10건 · P0 8 · P1 0)</t>
+        </is>
+      </c>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
+      <c r="H107" s="3"/>
+      <c r="I107" s="3"/>
     </row>
     <row r="108">
-      <c r="A108" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VIS-08</t>
-        </is>
-      </c>
-      <c r="B108" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I. 가시성</t>
-        </is>
-      </c>
-      <c r="C108" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">주간 자동 리포트</t>
-        </is>
-      </c>
-      <c r="D108" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E108" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="F108" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">공통</t>
-        </is>
-      </c>
-      <c r="G108" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VIS-05</t>
-        </is>
-      </c>
-      <c r="H108" s="8"/>
-      <c r="I108" s="8"/>
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SYS-01</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">J. 공통·기반</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alembic 마이그레이션</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세현</t>
+        </is>
+      </c>
+      <c r="G108" s="4"/>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">create_all() 의존을 제거한다. 컬럼 추가가 데이터 유실 없이 반영된다</t>
+        </is>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0 착수 전 완료</t>
+        </is>
+      </c>
     </row>
     <row r="109">
-      <c r="A109" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VIS-09</t>
-        </is>
-      </c>
-      <c r="B109" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I. 가시성</t>
-        </is>
-      </c>
-      <c r="C109" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">활동 타임라인</t>
-        </is>
-      </c>
-      <c r="D109" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E109" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F109" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">공통</t>
-        </is>
-      </c>
-      <c r="G109" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TSK-09</t>
-        </is>
-      </c>
-      <c r="H109" s="8"/>
-      <c r="I109" s="8"/>
-    </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">J. 공통·기반   (10건 · P0 8 · P1 0)</t>
-        </is>
-      </c>
-      <c r="B110" s="3"/>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3"/>
-      <c r="E110" s="3"/>
-      <c r="F110" s="3"/>
-      <c r="G110" s="3"/>
-      <c r="H110" s="3"/>
-      <c r="I110" s="3"/>
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SYS-02</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">J. 공통·기반</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Celery + Redis</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세현</t>
+        </is>
+      </c>
+      <c r="G109" s="4"/>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">워커가 죽어도 작업이 큐에 남고 재시작 시 이어진다</t>
+        </is>
+      </c>
+      <c r="I109" s="4"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SYS-03</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">J. 공통·기반</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에러코드 체계</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">확장</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세현</t>
+        </is>
+      </c>
+      <c r="G110" s="4"/>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기존 11종에 인증·권한·프로젝트 코드를 추가. 응답 형식이 일관된다</t>
+        </is>
+      </c>
+      <c r="I110" s="4"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SYS-01</t>
+          <t xml:space="preserve">SYS-04</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -4614,12 +4595,12 @@
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alembic 마이그레이션</t>
+          <t xml:space="preserve">request_id 로깅</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규</t>
+          <t xml:space="preserve">기존</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -4635,19 +4616,15 @@
       <c r="G111" s="4"/>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">create_all() 의존을 제거한다. 컬럼 추가가 데이터 유실 없이 반영된다</t>
-        </is>
-      </c>
-      <c r="I111" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P0 착수 전 완료</t>
-        </is>
-      </c>
+          <t xml:space="preserve">요청 단위로 로그 추적 가능</t>
+        </is>
+      </c>
+      <c r="I111" s="4"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SYS-02</t>
+          <t xml:space="preserve">SYS-05</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
@@ -4657,12 +4634,12 @@
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Celery + Redis</t>
+          <t xml:space="preserve">Fake AI Client</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규</t>
+          <t xml:space="preserve">기존</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -4678,54 +4655,58 @@
       <c r="G112" s="4"/>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">워커가 죽어도 작업이 큐에 남고 재시작 시 이어진다</t>
-        </is>
-      </c>
-      <c r="I112" s="4"/>
+          <t xml:space="preserve">API 키 없이 전체 흐름이 동작한다</t>
+        </is>
+      </c>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">병렬 작업의 전제</t>
+        </is>
+      </c>
     </row>
     <row r="113">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SYS-03</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="inlineStr">
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SYS-06</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">J. 공통·기반</t>
         </is>
       </c>
-      <c r="C113" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에러코드 체계</t>
-        </is>
-      </c>
-      <c r="D113" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">확장</t>
-        </is>
-      </c>
-      <c r="E113" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P0</t>
-        </is>
-      </c>
-      <c r="F113" s="5" t="inlineStr">
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API 호출 쿼터</t>
+        </is>
+      </c>
+      <c r="D113" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E113" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F113" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">세현</t>
         </is>
       </c>
-      <c r="G113" s="4"/>
-      <c r="H113" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기존 11종에 인증·권한·프로젝트 코드를 추가. 응답 형식이 일관된다</t>
-        </is>
-      </c>
-      <c r="I113" s="4"/>
+      <c r="G113" s="8"/>
+      <c r="H113" s="8"/>
+      <c r="I113" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로젝트별 월 한도</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SYS-04</t>
+          <t xml:space="preserve">SYS-07</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
@@ -4735,12 +4716,12 @@
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">request_id 로깅</t>
+          <t xml:space="preserve">N+1 방지</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">기존</t>
+          <t xml:space="preserve">신규</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -4756,15 +4737,19 @@
       <c r="G114" s="4"/>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">요청 단위로 로그 추적 가능</t>
-        </is>
-      </c>
-      <c r="I114" s="4"/>
+          <t xml:space="preserve">목록 조회 쿼리 수가 문서 수와 무관하게 일정하다. selectinload 사용</t>
+        </is>
+      </c>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미니 2+2N 해소</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SYS-05</t>
+          <t xml:space="preserve">SYS-08</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -4774,12 +4759,12 @@
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fake AI Client</t>
+          <t xml:space="preserve">FK 인덱스</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">기존</t>
+          <t xml:space="preserve">신규</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -4792,223 +4777,618 @@
           <t xml:space="preserve">세현</t>
         </is>
       </c>
-      <c r="G115" s="4"/>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SYS-01</t>
+        </is>
+      </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">API 키 없이 전체 흐름이 동작한다</t>
-        </is>
-      </c>
-      <c r="I115" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">병렬 작업의 전제</t>
-        </is>
-      </c>
+          <t xml:space="preserve">모든 FK 에 명시적 인덱스. PostgreSQL 은 자동 생성하지 않는다</t>
+        </is>
+      </c>
+      <c r="I115" s="4"/>
     </row>
     <row r="116">
-      <c r="A116" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SYS-06</t>
-        </is>
-      </c>
-      <c r="B116" s="8" t="inlineStr">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SYS-09</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">J. 공통·기반</t>
         </is>
       </c>
-      <c r="C116" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">API 호출 쿼터</t>
-        </is>
-      </c>
-      <c r="D116" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E116" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F116" s="10" t="inlineStr">
+      <c r="C116" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에러 로그 누락 수정</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">확장</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">세현</t>
         </is>
       </c>
-      <c r="G116" s="8"/>
-      <c r="H116" s="8"/>
-      <c r="I116" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프로젝트별 월 한도</t>
+      <c r="G116" s="4"/>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">404·409·413 이 서버 로그에 남는다</t>
+        </is>
+      </c>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미니 ISS-046. 첫날 수정</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SYS-07</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
+      <c r="A117" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SYS-10</t>
+        </is>
+      </c>
+      <c r="B117" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">J. 공통·기반</t>
         </is>
       </c>
-      <c r="C117" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N+1 방지</t>
-        </is>
-      </c>
-      <c r="D117" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P0</t>
-        </is>
-      </c>
-      <c r="F117" s="5" t="inlineStr">
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로컬 sLLM 옵션</t>
+        </is>
+      </c>
+      <c r="D117" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E117" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="F117" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">세현</t>
         </is>
       </c>
-      <c r="G117" s="4"/>
-      <c r="H117" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">목록 조회 쿼리 수가 문서 수와 무관하게 일정하다. selectinload 사용</t>
-        </is>
-      </c>
-      <c r="I117" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미니 2+2N 해소</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SYS-08</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">J. 공통·기반</t>
-        </is>
-      </c>
-      <c r="C118" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK 인덱스</t>
-        </is>
-      </c>
-      <c r="D118" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E118" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P0</t>
-        </is>
-      </c>
-      <c r="F118" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세현</t>
-        </is>
-      </c>
-      <c r="G118" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SYS-01</t>
-        </is>
-      </c>
-      <c r="H118" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">모든 FK 에 명시적 인덱스. PostgreSQL 은 자동 생성하지 않는다</t>
-        </is>
-      </c>
-      <c r="I118" s="4"/>
+      <c r="G117" s="8"/>
+      <c r="H117" s="8"/>
+      <c r="I117" s="8"/>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K. 산출물   (11건 · P0 0 · P1 9)</t>
+        </is>
+      </c>
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="3"/>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3"/>
+      <c r="H118" s="3"/>
+      <c r="I118" s="3"/>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SYS-09</t>
+          <t xml:space="preserve">DLV-01</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">J. 공통·기반</t>
+          <t xml:space="preserve">K. 산출물</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">에러 로그 누락 수정</t>
+          <t xml:space="preserve">산출물 페이지 (사이드바 메뉴)</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">확장</t>
+          <t xml:space="preserve">신규</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
-        </is>
-      </c>
-      <c r="G119" s="4"/>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRJ-01</t>
+        </is>
+      </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">404·409·413 이 서버 로그에 남는다</t>
+          <t xml:space="preserve">사이드바에 '산출물' 메뉴가 있고 개수 배지가 붙는다</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">미니 ISS-046. 첫날 수정</t>
+          <t xml:space="preserve">대시보드와 분리한다 — 이력 성격</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SYS-10</t>
-        </is>
-      </c>
-      <c r="B120" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">J. 공통·기반</t>
-        </is>
-      </c>
-      <c r="C120" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">로컬 sLLM 옵션</t>
-        </is>
-      </c>
-      <c r="D120" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E120" s="10" t="inlineStr">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-02</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K. 산출물</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기간 선택</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-01</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이번 주·지난 주·이번 달·직접 지정. 기간이 필요 없는 종류는 선택이 흐려진다</t>
+        </is>
+      </c>
+      <c r="I120" s="4"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-03</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K. 산출물</t>
+        </is>
+      </c>
+      <c r="C121" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성 대상 미리보기</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-02</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">선택한 기간에 잡히는 문서·완료 태스크·결정·기한·금액 건수가 LLM 호출 전에 보인다. 승인 대기 건수도 함께</t>
+        </is>
+      </c>
+      <c r="I121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">빈 보고서 방지 + 비용 절약 + 승인 유도</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-04</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K. 산출물</t>
+        </is>
+      </c>
+      <c r="C122" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주간 보고서 생성</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-03</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개요·문서 목록·태스크·결정·기한·금액 변동이 한 파일로 나온다. LLM 호출은 개요 한 단락에만 1회</t>
+        </is>
+      </c>
+      <c r="I122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tasks.completed_at 필수. 저장된 요약을 재요약한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-05</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K. 산출물</t>
+        </is>
+      </c>
+      <c r="C123" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정사항 대장 생성</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-14</t>
+        </is>
+      </c>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정 내용·결정일·출처 문서·상태(확정/미결/뒤집힘)가 표로 나온다</t>
+        </is>
+      </c>
+      <c r="I123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미니 프로젝트 결정사항 29건을 대신한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-06</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K. 산출물</t>
+        </is>
+      </c>
+      <c r="C124" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다음 회의 안건 생성</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-14</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decisions.status=PENDING 인 항목만 모아 안건으로 만든다</t>
+        </is>
+      </c>
+      <c r="I124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-05 의 부산물. 거의 공짜</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-07</t>
+        </is>
+      </c>
+      <c r="B125" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K. 산출물</t>
+        </is>
+      </c>
+      <c r="C125" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로젝트 현황 한 장</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E125" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F125" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G125" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-15</t>
+        </is>
+      </c>
+      <c r="H125" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">일정·태스크·결정·금액 현재 상태를 한 페이지로</t>
+        </is>
+      </c>
+      <c r="I125" s="8"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-08</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K. 산출물</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">형식 선택</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-01</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">XLSX·HTML·MD. 기본값이 없다. 고르지 않으면 생성 버튼이 비활성</t>
+        </is>
+      </c>
+      <c r="I126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_md2html.py·_build_wbs.py 재사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-09</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K. 산출물</t>
+        </is>
+      </c>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성 이력 · 다운로드</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-04</t>
+        </is>
+      </c>
+      <c r="H127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">만든 산출물이 목록으로 남고 다시 내려받을 수 있다</t>
+        </is>
+      </c>
+      <c r="I127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deliverables 테이블</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-10</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K. 산출물</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">갱신 필요 판정</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-09</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성 후 문서가 추가되면 '문서 N건이 나중에 추가됨' 과 다시 만들기가 표시된다</t>
+        </is>
+      </c>
+      <c r="I128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">source_counts_json 스냅샷 비교</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-11</t>
+        </is>
+      </c>
+      <c r="B129" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K. 산출물</t>
+        </is>
+      </c>
+      <c r="C129" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">인수인계 문서 생성</t>
+        </is>
+      </c>
+      <c r="D129" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E129" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">P3</t>
         </is>
       </c>
-      <c r="F120" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세현</t>
-        </is>
-      </c>
-      <c r="G120" s="8"/>
-      <c r="H120" s="8"/>
-      <c r="I120" s="8"/>
+      <c r="F129" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G129" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-07</t>
+        </is>
+      </c>
+      <c r="H129" s="8"/>
+      <c r="I129" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로젝트 종료 시 전체 누적</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:I120"/>
+  <autoFilter ref="A2:I129"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5017,8 +5397,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="78" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
@@ -5033,10 +5413,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
+    <row r="2" ht="46" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">구현 20일 (8/17~9/5 · 영업일 15일 · 3인 45 인일). P0+P1 을 다 못 하므로 '묶기' 로 접근한다. 근거 페이지 표시를 범위에서 빼면서 ANL-13(분석기 규격 확장)이 폐기되어 세 사람의 인터페이스 대기가 하나 줄었다.</t>
+          <t xml:space="preserve">구현 20일 (8/17~9/5 · 영업일 15일 · 3인 45 인일). P0+P1 을 다 못 하므로 '묶기' 로 접근한다. 설계가 크게 단순해졌다 — 분석기 선택 규칙·추계·단가 마스터·위치 하이라이트를 폐기하면서 세 사람이 서로 기다리는 지점이 사라졌다.</t>
         </is>
       </c>
     </row>
@@ -5081,7 +5461,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">A. 계정·권한</t>
+          <t xml:space="preserve">A. 계정·권한 (AUTH)</t>
         </is>
       </c>
       <c r="B5" s="5">
@@ -5108,7 +5488,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">B. 프로젝트</t>
+          <t xml:space="preserve">B. 프로젝트 (PRJ)</t>
         </is>
       </c>
       <c r="B6" s="5">
@@ -5135,7 +5515,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">C. 문서 입력·처리</t>
+          <t xml:space="preserve">C. 문서 입력·처리 (DOC)</t>
         </is>
       </c>
       <c r="B7" s="5">
@@ -5162,7 +5542,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">D. OCR 검수</t>
+          <t xml:space="preserve">D. OCR 검수 (REV)</t>
         </is>
       </c>
       <c r="B8" s="5">
@@ -5189,7 +5569,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">E. 일괄 처리</t>
+          <t xml:space="preserve">E. 일괄 처리 (BAT)</t>
         </is>
       </c>
       <c r="B9" s="5">
@@ -5216,17 +5596,17 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">F. 분석</t>
+          <t xml:space="preserve">F. 분석 (ANL)</t>
         </is>
       </c>
       <c r="B10" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" s="5">
         <v>4</v>
       </c>
       <c r="D10" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" s="5">
         <v>2</v>
@@ -5243,23 +5623,23 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">G. 금액·비용추계</t>
+          <t xml:space="preserve">G. 금액 (AMT)</t>
         </is>
       </c>
       <c r="B11" s="5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C11" s="5">
         <v>0</v>
       </c>
       <c r="D11" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E11" s="5">
         <v>2</v>
       </c>
       <c r="F11" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
@@ -5270,7 +5650,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">H. 태스크·협업</t>
+          <t xml:space="preserve">H. 태스크·협업 (TSK)</t>
         </is>
       </c>
       <c r="B12" s="5">
@@ -5297,11 +5677,11 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">I. 가시성</t>
+          <t xml:space="preserve">I. 가시성 (VIS)</t>
         </is>
       </c>
       <c r="B13" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" s="5">
         <v>0</v>
@@ -5313,7 +5693,7 @@
         <v>6</v>
       </c>
       <c r="F13" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
@@ -5324,7 +5704,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">J. 공통·기반</t>
+          <t xml:space="preserve">J. 공통·기반 (SYS)</t>
         </is>
       </c>
       <c r="B14" s="5">
@@ -5348,61 +5728,75 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K. 산출물 (DLV)</t>
+        </is>
+      </c>
+      <c r="B15" s="5">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>9</v>
+      </c>
+      <c r="E15" s="5">
+        <v>1</v>
+      </c>
+      <c r="F15" s="5">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">합계</t>
         </is>
       </c>
-      <c r="B15" s="3">
-        <v>108</v>
-      </c>
-      <c r="C15" s="3">
+      <c r="B16" s="3">
+        <v>116</v>
+      </c>
+      <c r="C16" s="3">
         <v>35</v>
       </c>
-      <c r="D15" s="3">
-        <v>37</v>
-      </c>
-      <c r="E15" s="3">
-        <v>24</v>
-      </c>
-      <c r="F15" s="3">
-        <v>12</v>
-      </c>
-      <c r="G15" s="3"/>
-    </row>
-    <row r="16"/>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="D16" s="3">
+        <v>45</v>
+      </c>
+      <c r="E16" s="3">
+        <v>25</v>
+      </c>
+      <c r="F16" s="3">
+        <v>11</v>
+      </c>
+      <c r="G16" s="3"/>
+    </row>
+    <row r="17"/>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">우선순위 정의</t>
         </is>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P0</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MVP 필수. 없으면 '팀 도구' 가 성립하지 않는다</t>
-        </is>
-      </c>
-      <c r="C18" s="4"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">차별화 핵심. 발표 데모의 중심</t>
+          <t xml:space="preserve">MVP 필수. 없으면 '팀 도구' 가 성립하지 않는다</t>
         </is>
       </c>
       <c r="C19" s="4"/>
@@ -5410,12 +5804,12 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">확장. 없어도 데모가 성립한다</t>
+          <t xml:space="preserve">차별화 핵심. 발표 데모의 중심</t>
         </is>
       </c>
       <c r="C20" s="4"/>
@@ -5423,48 +5817,48 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">확장. 없어도 데모가 성립한다</t>
+        </is>
+      </c>
+      <c r="C21" s="4"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">P3</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">향후. 발표에서 '향후 개선사항' 으로 배치한다</t>
         </is>
       </c>
-      <c r="C21" s="4"/>
-    </row>
-    <row r="22"/>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="C22" s="4"/>
+    </row>
+    <row r="23"/>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">묶음 — 같은 골격을 쓰므로 함께 만들면 두 번째부터 싸다</t>
         </is>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제안 골격</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANL-03 AMT-01 TSK-03 TSK-04 TSK-05 TSK-07 TSK-08 — 제안 카드·승인·역추적 UI 를 공유한다. 분석기만 갈아 끼운다</t>
-        </is>
-      </c>
-      <c r="C24" s="4"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">검수 골격</t>
+          <t xml:space="preserve">제안 골격</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">REV-01~REV-07 REV-16~REV-18 — 박스 표시와 텍스트 수정이 하나로 묶인다</t>
+          <t xml:space="preserve">ANL-03 ANL-14 ANL-15 AMT-01 TSK-03~TSK-08 — 제안 카드·승인·태스크 등록 UI 를 공유한다. 분석기만 갈아 끼운다</t>
         </is>
       </c>
       <c r="C25" s="4"/>
@@ -5472,15 +5866,41 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">산출물 골격</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-01~DLV-10 — 기간 필터·파일 생성·이력이 하나로 묶인다. 종류만 늘린다</t>
+        </is>
+      </c>
+      <c r="C26" s="4"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검수 골격</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REV-01~REV-07 REV-16~REV-18 — 박스 표시와 텍스트 수정이 하나로 묶인다</t>
+        </is>
+      </c>
+      <c r="C27" s="4"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">스코프</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">AUTH-* PRJ-* — 인증 없이 스코프가 성립하지 않는다</t>
         </is>
       </c>
-      <c r="C26" s="4"/>
+      <c r="C28" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
@@ -5491,25 +5911,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="34" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석기 선택 규칙 (ANL-04)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="46" customHeight="1">
+          <t xml:space="preserve">분석기 구성 — 4개, gather 한 번</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">문서 유형에 따라 실행할 분석기를 정한다. FastAPI 라우터와는 무관한 층이다. 유형은 업로드할 때 정해진다(DOC-16) — 사람이 고르면 분류 분석기를 건너뛰고, 자동 판별을 고르면 분류만 먼저 실행해 확정값을 만든다. 이렇게 해야 '분류는 분석 결과인데 선택은 분석 전' 인 순환이 풀린다.</t>
+          <t xml:space="preserve">문서 유형으로 분석기를 고르지 않는다. 항상 넷 다 돌린다. 회의록·보고서에도 금액이 나오므로 유형으로 껐다 켜면 놓치고, 분류를 먼저 돌리면 asyncio.gather 가 두 단계로 쪼개져 병렬성이 깨진다. 그래서 ANL-04 분석기 선택 규칙을 폐기했다. FastAPI 라우터와는 무관한 층이었다.</t>
         </is>
       </c>
     </row>
@@ -5517,264 +5938,302 @@
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문서 유형 (document_type) — 7종</t>
+          <t xml:space="preserve">registry 키</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">이름</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무엇을 뽑나</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">입력 토큰</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">출력 토큰</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기능 ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">summary</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">요약</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기존 — 코드 무수정</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요약문</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">약 2,800</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">약 125</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">category</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">분류</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">액션아이템</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">확장 — 7종 + reason</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유형 + 판단 근거</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">약 2,850</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">약 60</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">extract</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">항목 추출</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">액션아이템 · 결정 · 일정 배열</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">약 2,900</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">약 250</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-03 · ANL-14 · ANL-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amount</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">금액</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prompt_variant</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">계약서 CONTRACT</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">자동일 때만</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조항 검토</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O — 계약금액</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">contract_v1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">계약변경 CONTRACT_CHANGE</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">자동일 때만</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조항 검토</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O — 증감액</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">change_v1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">회의록 MEETING_NOTES</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">자동일 때만</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비용 발생 요인만</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">meeting_v1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">보고서 REPORT</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">자동일 때만</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O</t>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">금액 항목 배열</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">진행률 대비</t>
+          <t xml:space="preserve">약 2,850</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">report_v1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">공지사항 NOTICE</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">자동일 때만</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">메뉴얼 MANUAL</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">자동일 때만</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 ETC</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">자동일 때만</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prompt_variant 가 필요한 이유 — 같은 분석기라도 문서 유형에 따라 프롬프트가 달라야 한다. 액션아이템은 회의록(담당자·기한 중심)과 계약서(조항 검토 중심)가 다르고, 금액은 계약서(계약금액)와 계약변경(증감액)이 다르다. 계약변경을 별도 유형으로 나눈 이유가 이것이다 — 프롬프트가 스스로 판단하게 하면 그게 또 하나의 분류 문제가 되고 틀렸을 때 사람이 고칠 방법이 없다.</t>
+          <t xml:space="preserve">약 150</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMT-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">합계</t>
+        </is>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">약 11,400</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">약 585</t>
+        </is>
+      </c>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10"/>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">통합 1개와 비교 — 4개를 고른 이유</t>
+        </is>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">입력 토큰</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4개 약 11,400 / 통합 약 2,850. 통합이 75% 싸다 — 본문을 한 번만 보낸다</t>
+        </is>
+      </c>
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기존 코드</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4개는 요약·분류를 0줄 고친다 / 통합은 흡수하며 회귀 위험</t>
+        </is>
+      </c>
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">실패 단위</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4개는 하나 실패해도 나머지가 살아남는다 / 통합은 전부 실패</t>
+        </is>
+      </c>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">금액 정확도</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4개는 프롬프트를 집중할 수 있다 / 통합은 주의가 분산된다</t>
+        </is>
+      </c>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프롬프트 버전</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4개는 분석기별로 따로 올린다 / 통합은 하나로 뭉친다</t>
+        </is>
+      </c>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결론</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">토큰 2배를 감수하고 4개로 간다. 개발은 USE_FAKE_AI 로 하고 실제 호출은 데모·측정 때만이다. 통합 방식은 측정해서 비교하고 발표 소재로 쓴다</t>
+        </is>
+      </c>
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18"/>
+    <row r="19" ht="44" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">분석기 하나를 추가하는 비용 — 새 클래스 + 프롬프트 + dependencies.py 한 줄 + AnalyzerType 값. 라우터·서비스·스키마는 안 고친다 (analysis_router 가 analyzer_types 를 그대로 넘기고 analyses.analyzer_type 이 String(30) 이라 DB 변경도 없다).</t>
         </is>
       </c>
     </row>
@@ -5788,9 +6247,9 @@
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="46" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="32" customWidth="1"/>
+    <col min="2" max="2" width="44" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -5819,7 +6278,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">관련</t>
+          <t xml:space="preserve">비고</t>
         </is>
       </c>
     </row>
@@ -5866,42 +6325,42 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">동시성</t>
+          <t xml:space="preserve">성능</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4~5인 동시 사용 시 정상 동작</t>
+          <t xml:space="preserve">주간 보고서 생성 ≤ 15초</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">동시 업로드 5건</t>
-        </is>
-      </c>
-      <c r="D6" s="4"/>
+          <t xml:space="preserve">LLM 1회 + DB 쿼리</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-04</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">정확도</t>
+          <t xml:space="preserve">동시성</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">액션아이템 승인율 ≥ 70%</t>
+          <t xml:space="preserve">4~5인 동시 사용 시 정상 동작</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TSK-07 거부 기록 기반</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TSK-07</t>
-        </is>
-      </c>
+          <t xml:space="preserve">동시 업로드 5건</t>
+        </is>
+      </c>
+      <c r="D7" s="4"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -5911,15 +6370,19 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">카테고리 분류 정확도 ≥ 85%</t>
+          <t xml:space="preserve">액션아이템 승인율 ≥ 70%</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Golden Dataset</t>
-        </is>
-      </c>
-      <c r="D8" s="4"/>
+          <t xml:space="preserve">TSK-07 거부 기록 기반</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSK-07</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -5929,17 +6392,17 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">금액 항목 추출 정확도</t>
+          <t xml:space="preserve">카테고리 분류 정확도 ≥ 85%</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Golden Dataset · 원문 대조</t>
+          <t xml:space="preserve">document_type_source=USER_CORRECTED 비율</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">원문이 정답이라 측정 가능</t>
+          <t xml:space="preserve">정답셋 대신 실사용 데이터</t>
         </is>
       </c>
     </row>
@@ -5951,131 +6414,147 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">금액 계산 정확도 = 100%</t>
+          <t xml:space="preserve">일정 추출 정확도</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">단위테스트</t>
+          <t xml:space="preserve">Golden Dataset · 원문 대조</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Python 이 계산하므로 AI 지표가 아니다</t>
+          <t xml:space="preserve">날짜는 형식이 있다</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보안</t>
+          <t xml:space="preserve">정확도</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">타 프로젝트 데이터 접근 차단</t>
+          <t xml:space="preserve">금액 항목 추출 정확도</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRJ-08 침투 테스트</t>
+          <t xml:space="preserve">Golden Dataset · 원문 대조</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRJ-08</t>
+          <t xml:space="preserve">원문이 정답이다</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보안</t>
+          <t xml:space="preserve">정확도</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">API 키는 서버에만</t>
+          <t xml:space="preserve">금액 집계 정확도 = 100%</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">프론트 번들 검사</t>
-        </is>
-      </c>
-      <c r="D12" s="4"/>
+          <t xml:space="preserve">단위테스트</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">코드가 계산하므로 AI 지표가 아니다</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">보안</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">타 프로젝트 데이터 접근 차단</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRJ-08 침투 테스트</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRJ-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보안</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API 키는 서버에만</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프론트 번들 검사</t>
+        </is>
+      </c>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">안정성</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">컨테이너 재기동 후 파일 유지</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">재기동 후 다운로드</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DOC-14</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="16"/>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">하지 않을 것</t>
         </is>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4"/>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">실시간 공동 편집</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Notion·Google Docs 대체가 아니다</t>
-        </is>
-      </c>
-      <c r="D16" s="4"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4"/>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">간트 차트 등 본격 PMS</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">범위 밖</t>
-        </is>
-      </c>
-      <c r="D17" s="4"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="4"/>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">사람이 원가를 입력하는 비용 관리 모듈</t>
+          <t xml:space="preserve">실시간 공동 편집</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">컨셉과 반대다. 우리는 문서에서 뽑는다</t>
+          <t xml:space="preserve">Notion·Google Docs 대체가 아니다</t>
         </is>
       </c>
       <c r="D18" s="4"/>
@@ -6084,12 +6563,12 @@
       <c r="A19" s="4"/>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">모바일 네이티브 앱</t>
+          <t xml:space="preserve">간트 차트 등 본격 PMS</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">반응형 웹으로 대응</t>
+          <t xml:space="preserve">범위 밖</t>
         </is>
       </c>
       <c r="D19" s="4"/>
@@ -6098,12 +6577,12 @@
       <c r="A20" s="4"/>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">법안 등 법률문서 자동 생성</t>
+          <t xml:space="preserve">사람이 원가를 입력하는 비용 관리 모듈</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">환각 위험·법적 책임·검증 부담</t>
+          <t xml:space="preserve">컨셉과 반대다. 우리는 문서에서 뽑는다. 경계는 '입력을 누가 하는가'</t>
         </is>
       </c>
       <c r="D20" s="4"/>
@@ -6112,23 +6591,71 @@
       <c r="A21" s="4"/>
       <c r="B21" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">금액 추계 · 예측</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">없는 값을 만드는 일이다. 단가 근거를 댈 수 없다</t>
+        </is>
+      </c>
+      <c r="D21" s="4"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4"/>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모바일 네이티브 앱</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반응형 웹으로 대응</t>
+        </is>
+      </c>
+      <c r="D22" s="4"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4"/>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">법안 등 법률문서 자동 생성</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">환각 위험·법적 책임·검증 부담</t>
+        </is>
+      </c>
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4"/>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">파인튜닝</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">20일에 자리가 없다. 프롬프트 + 구조화 출력으로 목표 달성 가능</t>
         </is>
       </c>
-      <c r="D21" s="4"/>
-    </row>
-    <row r="22"/>
-    <row r="23" ht="44" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">'사람이 원가를 입력하는 모듈' 과 '문서에서 뽑은 금액 집계·검증' 의 경계를 분명히 한다. 차이는 입력을 사람이 하는가 문서가 하는가다.</t>
-        </is>
-      </c>
+      <c r="D24" s="4"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원문 위치 하이라이트</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">분석기 규격을 바꿔야 해서 세 사람이 서로 기다린다</t>
+        </is>
+      </c>
+      <c r="D25" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
@@ -6140,9 +6667,335 @@
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="66" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">폐기한 기능 — 번호를 재사용하지 않는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">왜 뺐는지가 결정 이력이다. 미니 프로젝트에서 결정사항에 미채택 대안과 이유를 남긴 것과 같은 형식으로 관리한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기능 ID</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기능명</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">영역</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">왜 폐기했나</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-04</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">분석기 선택 규칙 (analyzer_rules)</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F. 분석</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">회의록·보고서에도 금액이 나온다. 유형으로 껐다 켜면 오히려 놓친다. 그리고 분류를 먼저 돌려야 해서 asyncio.gather 가 두 단계로 쪼개져 병렬성이 깨졌다</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-13</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analyzer Protocol 위치 컨텍스트 확장</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F. 분석</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">근거를 페이지·좌표 대신 reason(판단 근거 서술)으로 표시하기로 해서 규격을 고칠 필요가 없어졌다. 세 사람의 인터페이스 대기가 하나 줄었다</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMT-04</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">단가 마스터 관리</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G. 금액</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">추계를 버리고 집계로 좁혀서 단가가 필요 없어졌다. 최대 위험이 통째로 사라졌다</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMT-05</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전제 입력 · 승인</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G. 금액</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMT-04 와 같은 이유</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMT-10</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비용추계서 서식 출력</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G. 금액</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">국회 의안 서식은 타깃 사용자(SI·스타트업·공공사업 수행팀)와 맞지 않는다. 향후 개선사항으로 배치</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIS-08</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주간 자동 리포트</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I. 가시성</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">폐기가 아니라 이동. DLV-04 로 옮기고 P3 -&gt; P1 로 승격했다</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">함께 없앤 테이블</t>
+        </is>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4"/>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">analyzer_rules · unit_prices · cost_estimates · cost_estimate_lines</t>
+        </is>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14"/>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">폐기하지 않고 성격만 바꾼 것</t>
+        </is>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DOC-16</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">분석기 선택 기준을 만든다</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">→</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목록 필터 · 프롬프트 힌트 · 산출물 분류</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-10</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">분석기별 채택률</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">→</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제안 종류별 채택률</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSK-04</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원문 위치 하이라이트</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">→</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">출처 문서 링크 + reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMT-06</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">추계 계산</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">→</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로젝트 금액 집계</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIS-08</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주간 자동 리포트 (P3)</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">→</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-04 로 이동해 P1 승격</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="5" customWidth="1"/>
     <col min="3" max="3" width="48" customWidth="1"/>
-    <col min="4" max="4" width="58" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
@@ -6204,12 +7057,12 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0+P1 78개, 구현 20일. 덜어내기보다 묶기로 접근</t>
+          <t xml:space="preserve">P0+P1 을 20일에 다 못 한다</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">요약 시트 묶음 3개 참고</t>
+          <t xml:space="preserve">덜어내기보다 묶기로 접근 (요약 시트)</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -6231,12 +7084,12 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">액션아이템(ANL-03)과 금액(AMT-01) 중 무엇을 먼저</t>
+          <t xml:space="preserve">ANL-03 항목 추출과 AMT-01 금액 중 무엇을 먼저</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">액션아이템으로 골격 → 금액을 두 번째 분석기로</t>
+          <t xml:space="preserve">ANL-03 으로 제안 골격을 만들고 금액을 두 번째로 얹는다</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -6263,7 +7116,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1단계만으로 금액 파트는 성립한다</t>
+          <t xml:space="preserve">1단계만으로도 금액·산출물 파트는 성립한다</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -6277,7 +7130,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">결정됨</t>
+          <t xml:space="preserve">우선순위</t>
         </is>
       </c>
       <c r="B7" s="5">
@@ -6285,12 +7138,12 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">근거 페이지·좌표 하이라이트 범위 제외</t>
+          <t xml:space="preserve">DLV 산출물 영역을 P1 로 두는 데 동의하는지</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">확정 — reason(판단 근거 서술)만 표시. ANL-13 폐기</t>
+          <t xml:space="preserve">동의 필요. 이게 없으면 '태스크 모음으로 뭘 하나' 에 답이 없다</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -6304,7 +7157,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">결정됨</t>
+          <t xml:space="preserve">DB</t>
         </is>
       </c>
       <c r="B8" s="5">
@@ -6312,17 +7165,17 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">문서 유형을 업로드 시 지정 (기본값 자동 판별)</t>
+          <t xml:space="preserve">tasks.completed_at · updated_at 추가</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">확정 — DOC-16. 일괄은 배치 단위 지정</t>
+          <t xml:space="preserve">필수. 없으면 DLV-04 주간 보고서를 만들 수 없다. 목업이 이미 '3월 7일 완료' 를 표시한다</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">전원</t>
+          <t xml:space="preserve">세현</t>
         </is>
       </c>
       <c r="F8" s="4"/>
@@ -6331,7 +7184,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">설계</t>
+          <t xml:space="preserve">DB</t>
         </is>
       </c>
       <c r="B9" s="5">
@@ -6339,12 +7192,12 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">파이프라인 단계 일반화 (ANL-05)</t>
+          <t xml:space="preserve">tasks.source_amount_item_id 추가</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">목업·프론트·enum·백엔드 4곳이 걸린다</t>
+          <t xml:space="preserve">필수. 출처 2갈래 + CHECK 제약</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -6358,7 +7211,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">결정됨</t>
+          <t xml:space="preserve">DB</t>
         </is>
       </c>
       <c r="B10" s="5">
@@ -6366,17 +7219,17 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">문서 유형을 7종으로 (계약변경 추가)</t>
+          <t xml:space="preserve">documents.document_type 7종 enum 실제 사용</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">확정 — 원계약은 계약금액, 변경합의서는 증감액. 프롬프트가 다르다</t>
+          <t xml:space="preserve">필수</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">전원</t>
+          <t xml:space="preserve">세현</t>
         </is>
       </c>
       <c r="F10" s="4"/>
@@ -6385,7 +7238,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">설계</t>
+          <t xml:space="preserve">DB</t>
         </is>
       </c>
       <c r="B11" s="5">
@@ -6393,12 +7246,12 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">분류가 틀렸을 때 사람이 document_type 을 고칠 수 있게 할지</t>
+          <t xml:space="preserve">documents.document_type_source 추가</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">허용. document_type_source=USER_CORRECTED 로 기록하면 분류 오류율이 나온다</t>
+          <t xml:space="preserve">선택. USER_CORRECTED 비율이 곧 분류 오류율</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -6412,7 +7265,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">설계</t>
+          <t xml:space="preserve">DB</t>
         </is>
       </c>
       <c r="B12" s="5">
@@ -6420,12 +7273,12 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">tasks 출처를 nullable FK 2개로 둘지</t>
+          <t xml:space="preserve">projects.started_on · due_on 추가</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK 무결성을 DB 가 보장한다. source_type+source_id 는 못 건다</t>
+          <t xml:space="preserve">선택. 일정 산출물용</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -6439,7 +7292,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">설계</t>
+          <t xml:space="preserve">DB</t>
         </is>
       </c>
       <c r="B13" s="5">
@@ -6447,17 +7300,17 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">제안 거부를 result_json.decision 에 둘지 별도 테이블로 둘지</t>
+          <t xml:space="preserve">activity_logs.action_type 값 목록</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">채택률 지표의 원천</t>
+          <t xml:space="preserve">팀 합의 필요. 주간 보고서 재료</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
+          <t xml:space="preserve">전원</t>
         </is>
       </c>
       <c r="F13" s="4"/>
@@ -6474,12 +7327,12 @@
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">analyzer_rules 를 테이블로 둘지 코드 상수로 둘지</t>
+          <t xml:space="preserve">분석기 4개 vs 통합 1개</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">테이블이면 설정 화면에 표로 보여줄 수 있다</t>
+          <t xml:space="preserve">4개로 시작. 측정 후 재검토</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -6501,17 +7354,17 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">단가 마스터 범위</t>
+          <t xml:space="preserve">VIEWER 에게 금액 노출 여부 (AMT-11)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMT 최대 위험. 소규모 자체 데이터로 고정하고 '데모 범위' 명시 권장</t>
+          <t xml:space="preserve">미결</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
+          <t xml:space="preserve">전원</t>
         </is>
       </c>
       <c r="F15" s="4"/>
@@ -6528,17 +7381,17 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIEWER 에게 금액 노출 여부 (AMT-11)</t>
+          <t xml:space="preserve">산출물 파일 저장 위치</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">노출 안 하면 조회 쿼리에 조건이 붙는다</t>
+          <t xml:space="preserve">DOC-14 S3·MinIO 와 같은 곳</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">전원</t>
+          <t xml:space="preserve">보현</t>
         </is>
       </c>
       <c r="F16" s="4"/>
@@ -6555,7 +7408,7 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">page_number 를 0 부터 셀지 1 부터 셀지</t>
+          <t xml:space="preserve">page_number 0 부터 · 1 부터</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -6582,7 +7435,7 @@
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">좌표 기준 이미지를 원본·렌더링본·전처리본 중 무엇으로</t>
+          <t xml:space="preserve">좌표 기준 이미지</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -6717,7 +7570,7 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">텍스트 재조립을 동기로 할지 비동기로 할지</t>
+          <t xml:space="preserve">텍스트 재조립 동기 · 비동기</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -6744,7 +7597,7 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">group_id 만 먼저 둘지 ocr_groups 를 처음부터 만들지</t>
+          <t xml:space="preserve">group_id 만 먼저 둘지</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -6771,7 +7624,7 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">재OCR 결과가 기존 박스를 자동 교체할지</t>
+          <t xml:space="preserve">재OCR 자동 교체 여부</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -6798,7 +7651,7 @@
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">오래된 분석을 자동 재실행할지</t>
+          <t xml:space="preserve">오래된 분석 자동 재실행</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -6857,7 +7710,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1조 사례로 보아 상용 API 유지 권장</t>
+          <t xml:space="preserve">상용 API 유지 권장. 1조가 Gemma 1B 에서 언어 쏠림을 겪었다</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">

--- a/산출물/기능명세서.xlsx
+++ b/산출물/기능명세서.xlsx
@@ -167,7 +167,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">DocFlow 기능명세서 — 유효 116건 (폐기 6건은 별도 시트)</t>
+          <t xml:space="preserve">DocFlow 기능명세서 — 유효 136건 (폐기 6건은 별도 시트)</t>
         </is>
       </c>
     </row>
@@ -261,7 +261,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G4" s="4"/>
@@ -300,7 +300,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -343,7 +343,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -429,7 +429,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -476,7 +476,7 @@
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G9" s="8"/>
@@ -526,7 +526,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G19" s="8"/>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G29" s="4"/>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G31" s="4"/>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G34" s="4"/>
@@ -2704,7 +2704,7 @@
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">F. 분석   (13건 · P0 4 · P1 5)</t>
+          <t xml:space="preserve">F. 분석   (15건 · P0 4 · P1 7)</t>
         </is>
       </c>
       <c r="B64" s="3"/>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
+          <t xml:space="preserve">세현</t>
         </is>
       </c>
       <c r="G65" s="4"/>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
+          <t xml:space="preserve">세현</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
+          <t xml:space="preserve">세현</t>
         </is>
       </c>
       <c r="G67" s="4"/>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
+          <t xml:space="preserve">세현</t>
         </is>
       </c>
       <c r="G68" s="4"/>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
+          <t xml:space="preserve">세현</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
+          <t xml:space="preserve">세현</t>
         </is>
       </c>
       <c r="G70" s="4"/>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
+          <t xml:space="preserve">세현</t>
         </is>
       </c>
       <c r="G71" s="4"/>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
+          <t xml:space="preserve">세현</t>
         </is>
       </c>
       <c r="G72" s="8"/>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
+          <t xml:space="preserve">세현</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
+          <t xml:space="preserve">세현</t>
         </is>
       </c>
       <c r="G74" s="8"/>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
+          <t xml:space="preserve">세현</t>
         </is>
       </c>
       <c r="G75" s="8"/>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
+          <t xml:space="preserve">세현</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
@@ -3252,54 +3252,86 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">세현</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-03</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문서의 날짜를 뽑아 schedule_items 에 쌓는다. 날짜는 형식이 있어 원문 대조로 정확도를 잴 수 있다</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-04·DLV-07 의 재료</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-16</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F. 분석</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구조화 출력 검증 · 재시도</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">보현</t>
         </is>
       </c>
-      <c r="G77" s="4" t="inlineStr">
+      <c r="G78" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ANL-03</t>
         </is>
       </c>
-      <c r="H77" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">문서의 날짜를 뽑아 schedule_items 에 쌓는다. 날짜는 형식이 있어 원문 대조로 정확도를 잴 수 있다</t>
-        </is>
-      </c>
-      <c r="I77" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DLV-04·DLV-07 의 재료</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G. 금액   (8건 · P0 0 · P1 6)</t>
-        </is>
-      </c>
-      <c r="B78" s="3"/>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="3"/>
-      <c r="G78" s="3"/>
-      <c r="H78" s="3"/>
-      <c r="I78" s="3"/>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모델이 형식을 어기면 검출해 재시도하고 실패가 로그에 남는다</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결과를 String 으로 먼저 받기로 해서 파싱 실패가 흔하다</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMT-01</t>
+          <t xml:space="preserve">ANL-17</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">G. 금액</t>
+          <t xml:space="preserve">F. 분석</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">금액 항목 추출</t>
+          <t xml:space="preserve">평가셋 기반 정확도 측정 자동화</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -3317,69 +3349,41 @@
           <t xml:space="preserve">보현</t>
         </is>
       </c>
-      <c r="G79" s="4"/>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-03</t>
+        </is>
+      </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">항목명·수량·단위·금액·reason 을 구조화 스키마로 반환. 문서에 없는 값은 비운다</t>
+          <t xml:space="preserve">정답 데이터와 대조해 정확도가 수치로 나온다. 모델·프롬프트를 바꿔도 같은 자로 잰다</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">LLM 은 추출만. 계산은 코드</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AMT-02</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G. 금액</t>
-        </is>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">금액 항목 승인 · 수정 UI</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">보현</t>
-        </is>
-      </c>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AMT-01</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">액션아이템과 같은 제안 카드 형식. 승인 전에는 어디에도 반영되지 않는다</t>
-        </is>
-      </c>
-      <c r="I80" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI 패턴 재사용</t>
-        </is>
-      </c>
+          <t xml:space="preserve">세현님 모델 비교에 직접 쓰인다</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G. 금액   (14건 · P0 0 · P1 10)</t>
+        </is>
+      </c>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="3"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMT-03</t>
+          <t xml:space="preserve">AMT-01</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -3389,7 +3393,7 @@
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">합계 대조</t>
+          <t xml:space="preserve">금액 항목 추출</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -3404,29 +3408,25 @@
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
-        </is>
-      </c>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AMT-01</t>
-        </is>
-      </c>
+          <t xml:space="preserve">세현</t>
+        </is>
+      </c>
+      <c r="G81" s="4"/>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">항목 합계와 문서에 적힌 합계가 다르면 불일치 금액과 함께 표시된다</t>
+          <t xml:space="preserve">항목명·수량·단위·금액·reason 을 구조화 스키마로 반환. 문서에 없는 값은 비운다</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">검증 가능한 유일한 기능</t>
+          <t xml:space="preserve">LLM 은 추출만. 계산은 코드</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMT-06</t>
+          <t xml:space="preserve">AMT-02</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">프로젝트 금액 집계</t>
+          <t xml:space="preserve">금액 항목 승인 · 수정 UI</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -3456,24 +3456,24 @@
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMT-02</t>
+          <t xml:space="preserve">AMT-01</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">여러 문서의 금액을 프로젝트 단위로 모은다. 같은 입력이면 항상 같은 결과가 나온다</t>
+          <t xml:space="preserve">액션아이템과 같은 제안 카드 형식. 승인 전에는 어디에도 반영되지 않는다</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">단위테스트로 확인. 추계가 아니라 집계</t>
+          <t xml:space="preserve">UI 패턴 재사용</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMT-07</t>
+          <t xml:space="preserve">AMT-03</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">불일치 태스크 제안</t>
+          <t xml:space="preserve">합계 대조</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -3503,63 +3503,71 @@
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TSK-03</t>
+          <t xml:space="preserve">AMT-01</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">불일치 시 태스크 제안 카드가 생긴다. 자동 등록은 하지 않는다</t>
-        </is>
-      </c>
-      <c r="I83" s="4"/>
+          <t xml:space="preserve">항목 합계와 문서에 적힌 합계가 다르면 불일치 금액과 함께 표시된다</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검증 가능한 유일한 기능</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AMT-08</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMT-06</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">G. 금액</t>
         </is>
       </c>
-      <c r="C84" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프로젝트 금액 현황</t>
-        </is>
-      </c>
-      <c r="D84" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E84" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F84" s="10" t="inlineStr">
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로젝트 금액 집계</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">보현</t>
         </is>
       </c>
-      <c r="G84" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AMT-06</t>
-        </is>
-      </c>
-      <c r="H84" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">계약금액·변경 증감·집행률·잔액이 프로젝트 단위로 보인다</t>
-        </is>
-      </c>
-      <c r="I84" s="8"/>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMT-02</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">여러 문서의 금액을 프로젝트 단위로 모은다. 같은 입력이면 항상 같은 결과가 나온다</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">단위테스트로 확인. 추계가 아니라 집계</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMT-09</t>
+          <t xml:space="preserve">AMT-07</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -3569,7 +3577,7 @@
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">금액 판단 근거 표시</t>
+          <t xml:space="preserve">불일치 태스크 제안</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -3589,135 +3597,163 @@
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMT-01</t>
+          <t xml:space="preserve">TSK-03</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">금액 항목마다 reason 이 보이고 출처 문서로 이동할 수 있다</t>
-        </is>
-      </c>
-      <c r="I85" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위치 하이라이트는 범위 밖</t>
-        </is>
-      </c>
+          <t xml:space="preserve">불일치 시 태스크 제안 카드가 생긴다. 자동 등록은 하지 않는다</t>
+        </is>
+      </c>
+      <c r="I85" s="4"/>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">AMT-08</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G. 금액</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로젝트 금액 현황</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F86" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G86" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMT-06</t>
+        </is>
+      </c>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">계약금액·변경 증감·집행률·잔액이 프로젝트 단위로 보인다</t>
+        </is>
+      </c>
+      <c r="I86" s="8"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMT-09</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G. 금액</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">금액 판단 근거 표시</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세현</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMT-01</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">금액 항목마다 reason 이 보이고 출처 문서로 이동할 수 있다</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">위치 하이라이트는 범위 밖</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">AMT-11</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">G. 금액</t>
         </is>
       </c>
-      <c r="C86" s="8" t="inlineStr">
+      <c r="C88" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">금액 열람 권한 분리</t>
         </is>
       </c>
-      <c r="D86" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E86" s="10" t="inlineStr">
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="F86" s="10" t="inlineStr">
+      <c r="F88" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">보현</t>
         </is>
       </c>
-      <c r="G86" s="8" t="inlineStr">
+      <c r="G88" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">PRJ-07</t>
         </is>
       </c>
-      <c r="H86" s="8"/>
-      <c r="I86" s="8" t="inlineStr">
+      <c r="H88" s="8"/>
+      <c r="I88" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">미결 — VIEWER 노출 여부</t>
         </is>
       </c>
-    </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">H. 태스크·협업   (10건 · P0 0 · P1 8)</t>
-        </is>
-      </c>
-      <c r="B87" s="3"/>
-      <c r="C87" s="3"/>
-      <c r="D87" s="3"/>
-      <c r="E87" s="3"/>
-      <c r="F87" s="3"/>
-      <c r="G87" s="3"/>
-      <c r="H87" s="3"/>
-      <c r="I87" s="3"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TSK-01</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">H. 태스크·협업</t>
-        </is>
-      </c>
-      <c r="C88" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">태스크 CRUD</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F88" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세현</t>
-        </is>
-      </c>
-      <c r="G88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRJ-01</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제목·설명·담당자·기한·상태를 사람이 직접 만들 수 있다</t>
-        </is>
-      </c>
-      <c r="I88" s="4"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TSK-02</t>
+          <t xml:space="preserve">AMT-12</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">H. 태스크·협업</t>
+          <t xml:space="preserve">G. 금액</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">칸반 보드</t>
+          <t xml:space="preserve">추출 결과 스키마 검증 · 정규화</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -3732,35 +3768,39 @@
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">보현</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TSK-01</t>
+          <t xml:space="preserve">AMT-01</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">할 일·진행 중·완료 3열, 열별 개수 표시, 드래그로 상태 변경</t>
-        </is>
-      </c>
-      <c r="I89" s="4"/>
+          <t xml:space="preserve">모델 응답이 계약 스키마에 맞는지 검사하고 어긋나면 AI_INVALID_RESPONSE 로 재시도한다</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">쉼표·단위 제거, 원 단위 정수화</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TSK-03</t>
+          <t xml:space="preserve">AMT-13</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">H. 태스크·협업</t>
+          <t xml:space="preserve">G. 금액</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI 제안 → 태스크 확정</t>
+          <t xml:space="preserve">단가 · 원가구분 컬럼 추가</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -3775,39 +3815,39 @@
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">보현</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-03</t>
+          <t xml:space="preserve">AMT-01</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">승인해야 등록된다. 승인 전에는 보드에 나타나지 않는다</t>
+          <t xml:space="preserve">unit_price 와 category 가 저장되고 부가세가 구분된다</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">자동 등록 금지 원칙</t>
+          <t xml:space="preserve">리비전 0008. 부가세를 구분 못 하면 합계가 틀린다</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TSK-04</t>
+          <t xml:space="preserve">AMT-14</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">H. 태스크·협업</t>
+          <t xml:space="preserve">G. 금액</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">출처 · 판단 근거 표시</t>
+          <t xml:space="preserve">비용 산출 엔진</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -3822,394 +3862,410 @@
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">보현</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TSK-03</t>
+          <t xml:space="preserve">AMT-13</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">태스크에 출처 문서 링크와 AI 판단 근거(reason)가 함께 보인다</t>
+          <t xml:space="preserve">수량 × 단가 계산과 항목 합계를 코드가 수행한다. LLM 은 계산에 관여하지 않는다</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">원문 위치 하이라이트는 범위 밖</t>
+          <t xml:space="preserve">결정론적. 같은 입력 같은 결과</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TSK-05</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">H. 태스크·협업</t>
-        </is>
-      </c>
-      <c r="C92" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AI 생성 배지 · 필터</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E92" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F92" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세현</t>
-        </is>
-      </c>
-      <c r="G92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TSK-03</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AI 생성 태스크가 구분 표시되고 AI생성만·기한임박·출처문서별 필터가 동작한다</t>
-        </is>
-      </c>
-      <c r="I92" s="4"/>
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMT-15</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G. 금액</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">근거 변경 탐지 및 재계산</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E92" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F92" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G92" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMT-14</t>
+        </is>
+      </c>
+      <c r="H92" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문서가 수정되면 변경된 필드만 다시 추출해 재계산한다. 모델 재학습은 없다</t>
+        </is>
+      </c>
+      <c r="I92" s="8"/>
     </row>
     <row r="93">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TSK-06</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">H. 태스크·협업</t>
-        </is>
-      </c>
-      <c r="C93" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">담당자 · 기한 지정</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세현</t>
-        </is>
-      </c>
-      <c r="G93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TSK-01</t>
-        </is>
-      </c>
-      <c r="H93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AI 가 못 찾은 경우 미지정 상태로 남고 사람이 채운다</t>
-        </is>
-      </c>
-      <c r="I93" s="4"/>
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMT-16</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G. 금액</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">계산 버전 · 변경 내역 저장</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E93" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F93" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMT-15</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변경 전후 값과 차액이 남아 어떤 근거로 금액이 바뀌었는지 추적된다</t>
+        </is>
+      </c>
+      <c r="I93" s="8"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TSK-07</t>
+          <t xml:space="preserve">AMT-17</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">G. 금액</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">계산식 · 산출 근거 표시</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMT-14</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">금액마다 계산식과 출처 문서 · 원문 인용이 함께 보인다</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMT-09 와 짝</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H. 태스크·협업   (10건 · P0 0 · P1 8)</t>
+        </is>
+      </c>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3"/>
+      <c r="I95" s="3"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSK-01</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">H. 태스크·협업</t>
         </is>
       </c>
-      <c r="C94" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제안 거부</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="inlineStr">
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">태스크 CRUD</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="F94" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세현</t>
-        </is>
-      </c>
-      <c r="G94" s="4" t="inlineStr">
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미정</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRJ-01</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제목·설명·담당자·기한·상태를 사람이 직접 만들 수 있다</t>
+        </is>
+      </c>
+      <c r="I96" s="4"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSK-02</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H. 태스크·협업</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">칸반 보드</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미정</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSK-01</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">할 일·진행 중·완료 3열, 열별 개수 표시, 드래그로 상태 변경</t>
+        </is>
+      </c>
+      <c r="I97" s="4"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">TSK-03</t>
         </is>
       </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">거부한 제안은 다시 뜨지 않는다. 거부 사실이 기록된다</t>
-        </is>
-      </c>
-      <c r="I94" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">채택률 지표의 원천</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TSK-08</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">H. 태스크·협업</t>
         </is>
       </c>
-      <c r="C95" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일괄 승인</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="inlineStr">
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI 제안 → 태스크 확정</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세현</t>
-        </is>
-      </c>
-      <c r="G95" s="4" t="inlineStr">
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미정</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-03</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">승인해야 등록된다. 승인 전에는 보드에 나타나지 않는다</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자동 등록 금지 원칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSK-04</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H. 태스크·협업</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">출처 · 판단 근거 표시</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미정</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">TSK-03</t>
         </is>
       </c>
-      <c r="H95" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">문서 단위로 여러 제안을 한 번에 승인할 수 있다</t>
-        </is>
-      </c>
-      <c r="I95" s="4"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TSK-09</t>
-        </is>
-      </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">태스크에 출처 문서 링크와 AI 판단 근거(reason)가 함께 보인다</t>
+        </is>
+      </c>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원문 위치 하이라이트는 범위 밖</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSK-05</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">H. 태스크·협업</t>
         </is>
       </c>
-      <c r="C96" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">활동 로그</t>
-        </is>
-      </c>
-      <c r="D96" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E96" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F96" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세현</t>
-        </is>
-      </c>
-      <c r="G96" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRJ-01</t>
-        </is>
-      </c>
-      <c r="H96" s="8"/>
-      <c r="I96" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">activity_logs. 주간 보고서 재료</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TSK-10</t>
-        </is>
-      </c>
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">H. 태스크·협업</t>
-        </is>
-      </c>
-      <c r="C97" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">알림 (이메일 · Slack)</t>
-        </is>
-      </c>
-      <c r="D97" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E97" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="F97" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세현</t>
-        </is>
-      </c>
-      <c r="G97" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TSK-09</t>
-        </is>
-      </c>
-      <c r="H97" s="8"/>
-      <c r="I97" s="8"/>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I. 가시성   (8건 · P0 0 · P1 1)</t>
-        </is>
-      </c>
-      <c r="B98" s="3"/>
-      <c r="C98" s="3"/>
-      <c r="D98" s="3"/>
-      <c r="E98" s="3"/>
-      <c r="F98" s="3"/>
-      <c r="G98" s="3"/>
-      <c r="H98" s="3"/>
-      <c r="I98" s="3"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VIS-01</t>
-        </is>
-      </c>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I. 가시성</t>
-        </is>
-      </c>
-      <c r="C99" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대시보드 지표 카드</t>
-        </is>
-      </c>
-      <c r="D99" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E99" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F99" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">공통</t>
-        </is>
-      </c>
-      <c r="G99" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRJ-01</t>
-        </is>
-      </c>
-      <c r="H99" s="8"/>
-      <c r="I99" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전체 문서·처리 중·열린 태스크·승인 대기</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VIS-02</t>
-        </is>
-      </c>
-      <c r="B100" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I. 가시성</t>
-        </is>
-      </c>
-      <c r="C100" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">문서 유형 분포</t>
-        </is>
-      </c>
-      <c r="D100" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E100" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F100" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">공통</t>
-        </is>
-      </c>
-      <c r="G100" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANL-02</t>
-        </is>
-      </c>
-      <c r="H100" s="8"/>
-      <c r="I100" s="8"/>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI 생성 배지 · 필터</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미정</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSK-03</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI 생성 태스크가 구분 표시되고 AI생성만·기한임박·출처문서별 필터가 동작한다</t>
+        </is>
+      </c>
+      <c r="I100" s="4"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIS-03</t>
+          <t xml:space="preserve">TSK-06</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">I. 가시성</t>
+          <t xml:space="preserve">H. 태스크·협업</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">승인 대기 배너</t>
+          <t xml:space="preserve">담당자 · 기한 지정</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
@@ -4224,121 +4280,125 @@
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">공통</t>
+          <t xml:space="preserve">미정</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">TSK-01</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI 가 못 찾은 경우 미지정 상태로 남고 사람이 채운다</t>
+        </is>
+      </c>
+      <c r="I101" s="4"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSK-07</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H. 태스크·협업</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제안 거부</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미정</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">TSK-03</t>
         </is>
       </c>
-      <c r="H101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">승인 대기 건수와 출처 문서명이 보이고 검토 화면으로 이동한다</t>
-        </is>
-      </c>
-      <c r="I101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제안 종류별로 나눠 표시</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VIS-04</t>
-        </is>
-      </c>
-      <c r="B102" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I. 가시성</t>
-        </is>
-      </c>
-      <c r="C102" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">최근 문서</t>
-        </is>
-      </c>
-      <c r="D102" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E102" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F102" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">공통</t>
-        </is>
-      </c>
-      <c r="G102" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DOC-08</t>
-        </is>
-      </c>
-      <c r="H102" s="8"/>
-      <c r="I102" s="8"/>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">거부한 제안은 다시 뜨지 않는다. 거부 사실이 기록된다</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">채택률 지표의 원천</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VIS-05</t>
-        </is>
-      </c>
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I. 가시성</t>
-        </is>
-      </c>
-      <c r="C103" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이번 주 활동</t>
-        </is>
-      </c>
-      <c r="D103" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E103" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F103" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">공통</t>
-        </is>
-      </c>
-      <c r="G103" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANL-10</t>
-        </is>
-      </c>
-      <c r="H103" s="8"/>
-      <c r="I103" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제안 종류별 채택률 포함</t>
-        </is>
-      </c>
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSK-08</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H. 태스크·협업</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">일괄 승인</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미정</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSK-03</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문서 단위로 여러 제안을 한 번에 승인할 수 있다</t>
+        </is>
+      </c>
+      <c r="I103" s="4"/>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIS-06</t>
+          <t xml:space="preserve">TSK-09</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">I. 가시성</t>
+          <t xml:space="preserve">H. 태스크·협업</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">통합 검색 (PostgreSQL FTS)</t>
+          <t xml:space="preserve">활동 로그</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
@@ -4353,35 +4413,35 @@
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">공통</t>
+          <t xml:space="preserve">미정</t>
         </is>
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRJ-08</t>
+          <t xml:space="preserve">PRJ-01</t>
         </is>
       </c>
       <c r="H104" s="8"/>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">프로젝트 스코프 안에서</t>
+          <t xml:space="preserve">activity_logs. 주간 보고서 재료</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIS-07</t>
+          <t xml:space="preserve">TSK-10</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">I. 가시성</t>
+          <t xml:space="preserve">H. 태스크·협업</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">시맨틱 검색 (pgvector)</t>
+          <t xml:space="preserve">알림 (이메일 · Slack)</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
@@ -4396,128 +4456,128 @@
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">공통</t>
+          <t xml:space="preserve">미정</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIS-06</t>
+          <t xml:space="preserve">TSK-09</t>
         </is>
       </c>
       <c r="H105" s="8"/>
       <c r="I105" s="8"/>
     </row>
-    <row r="106">
-      <c r="A106" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VIS-09</t>
-        </is>
-      </c>
-      <c r="B106" s="8" t="inlineStr">
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I. 가시성   (8건 · P0 0 · P1 1)</t>
+        </is>
+      </c>
+      <c r="B106" s="3"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3"/>
+      <c r="H106" s="3"/>
+      <c r="I106" s="3"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIS-01</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">I. 가시성</t>
         </is>
       </c>
-      <c r="C106" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">활동 타임라인</t>
-        </is>
-      </c>
-      <c r="D106" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E106" s="10" t="inlineStr">
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대시보드 지표 카드</t>
+        </is>
+      </c>
+      <c r="D107" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E107" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="F106" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">공통</t>
-        </is>
-      </c>
-      <c r="G106" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TSK-09</t>
-        </is>
-      </c>
-      <c r="H106" s="8"/>
-      <c r="I106" s="8"/>
-    </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">J. 공통·기반   (10건 · P0 8 · P1 0)</t>
-        </is>
-      </c>
-      <c r="B107" s="3"/>
-      <c r="C107" s="3"/>
-      <c r="D107" s="3"/>
-      <c r="E107" s="3"/>
-      <c r="F107" s="3"/>
-      <c r="G107" s="3"/>
-      <c r="H107" s="3"/>
-      <c r="I107" s="3"/>
+      <c r="F107" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G107" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRJ-01</t>
+        </is>
+      </c>
+      <c r="H107" s="8"/>
+      <c r="I107" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전체 문서·처리 중·열린 태스크·승인 대기</t>
+        </is>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SYS-01</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">J. 공통·기반</t>
-        </is>
-      </c>
-      <c r="C108" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Alembic 마이그레이션</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P0</t>
-        </is>
-      </c>
-      <c r="F108" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세현</t>
-        </is>
-      </c>
-      <c r="G108" s="4"/>
-      <c r="H108" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">create_all() 의존을 제거한다. 컬럼 추가가 데이터 유실 없이 반영된다</t>
-        </is>
-      </c>
-      <c r="I108" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P0 착수 전 완료</t>
-        </is>
-      </c>
+      <c r="A108" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIS-02</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I. 가시성</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문서 유형 분포</t>
+        </is>
+      </c>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E108" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F108" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G108" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-02</t>
+        </is>
+      </c>
+      <c r="H108" s="8"/>
+      <c r="I108" s="8"/>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SYS-02</t>
+          <t xml:space="preserve">VIS-03</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">J. 공통·기반</t>
+          <t xml:space="preserve">I. 가시성</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Celery + Redis</t>
+          <t xml:space="preserve">승인 대기 배너</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
@@ -4527,157 +4587,169 @@
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
-        </is>
-      </c>
-      <c r="G109" s="4"/>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSK-03</t>
+        </is>
+      </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">워커가 죽어도 작업이 큐에 남고 재시작 시 이어진다</t>
-        </is>
-      </c>
-      <c r="I109" s="4"/>
+          <t xml:space="preserve">승인 대기 건수와 출처 문서명이 보이고 검토 화면으로 이동한다</t>
+        </is>
+      </c>
+      <c r="I109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제안 종류별로 나눠 표시</t>
+        </is>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SYS-03</t>
-        </is>
-      </c>
-      <c r="B110" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">J. 공통·기반</t>
-        </is>
-      </c>
-      <c r="C110" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에러코드 체계</t>
-        </is>
-      </c>
-      <c r="D110" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">확장</t>
-        </is>
-      </c>
-      <c r="E110" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P0</t>
-        </is>
-      </c>
-      <c r="F110" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세현</t>
-        </is>
-      </c>
-      <c r="G110" s="4"/>
-      <c r="H110" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기존 11종에 인증·권한·프로젝트 코드를 추가. 응답 형식이 일관된다</t>
-        </is>
-      </c>
-      <c r="I110" s="4"/>
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIS-04</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I. 가시성</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최근 문서</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E110" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F110" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G110" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DOC-08</t>
+        </is>
+      </c>
+      <c r="H110" s="8"/>
+      <c r="I110" s="8"/>
     </row>
     <row r="111">
-      <c r="A111" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SYS-04</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">J. 공통·기반</t>
-        </is>
-      </c>
-      <c r="C111" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">request_id 로깅</t>
-        </is>
-      </c>
-      <c r="D111" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기존</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P0</t>
-        </is>
-      </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세현</t>
-        </is>
-      </c>
-      <c r="G111" s="4"/>
-      <c r="H111" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요청 단위로 로그 추적 가능</t>
-        </is>
-      </c>
-      <c r="I111" s="4"/>
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIS-05</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I. 가시성</t>
+        </is>
+      </c>
+      <c r="C111" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이번 주 활동</t>
+        </is>
+      </c>
+      <c r="D111" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E111" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F111" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G111" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-10</t>
+        </is>
+      </c>
+      <c r="H111" s="8"/>
+      <c r="I111" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제안 종류별 채택률 포함</t>
+        </is>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SYS-05</t>
-        </is>
-      </c>
-      <c r="B112" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">J. 공통·기반</t>
-        </is>
-      </c>
-      <c r="C112" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fake AI Client</t>
-        </is>
-      </c>
-      <c r="D112" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기존</t>
-        </is>
-      </c>
-      <c r="E112" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P0</t>
-        </is>
-      </c>
-      <c r="F112" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세현</t>
-        </is>
-      </c>
-      <c r="G112" s="4"/>
-      <c r="H112" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">API 키 없이 전체 흐름이 동작한다</t>
-        </is>
-      </c>
-      <c r="I112" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">병렬 작업의 전제</t>
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIS-06</t>
+        </is>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I. 가시성</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">통합 검색 (PostgreSQL FTS)</t>
+        </is>
+      </c>
+      <c r="D112" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E112" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F112" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G112" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRJ-08</t>
+        </is>
+      </c>
+      <c r="H112" s="8"/>
+      <c r="I112" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로젝트 스코프 안에서</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">SYS-06</t>
+          <t xml:space="preserve">VIS-07</t>
         </is>
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">J. 공통·기반</t>
+          <t xml:space="preserve">I. 가시성</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">API 호출 쿼터</t>
+          <t xml:space="preserve">시맨틱 검색 (pgvector)</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
@@ -4687,112 +4759,80 @@
       </c>
       <c r="E113" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="F113" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIS-06</t>
+        </is>
+      </c>
+      <c r="H113" s="8"/>
+      <c r="I113" s="8"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIS-09</t>
+        </is>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I. 가시성</t>
+        </is>
+      </c>
+      <c r="C114" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">활동 타임라인</t>
+        </is>
+      </c>
+      <c r="D114" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E114" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="F113" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세현</t>
-        </is>
-      </c>
-      <c r="G113" s="8"/>
-      <c r="H113" s="8"/>
-      <c r="I113" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프로젝트별 월 한도</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SYS-07</t>
-        </is>
-      </c>
-      <c r="B114" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">J. 공통·기반</t>
-        </is>
-      </c>
-      <c r="C114" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N+1 방지</t>
-        </is>
-      </c>
-      <c r="D114" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E114" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P0</t>
-        </is>
-      </c>
-      <c r="F114" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세현</t>
-        </is>
-      </c>
-      <c r="G114" s="4"/>
-      <c r="H114" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">목록 조회 쿼리 수가 문서 수와 무관하게 일정하다. selectinload 사용</t>
-        </is>
-      </c>
-      <c r="I114" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미니 2+2N 해소</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SYS-08</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">J. 공통·기반</t>
-        </is>
-      </c>
-      <c r="C115" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK 인덱스</t>
-        </is>
-      </c>
-      <c r="D115" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E115" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P0</t>
-        </is>
-      </c>
-      <c r="F115" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세현</t>
-        </is>
-      </c>
-      <c r="G115" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SYS-01</t>
-        </is>
-      </c>
-      <c r="H115" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">모든 FK 에 명시적 인덱스. PostgreSQL 은 자동 생성하지 않는다</t>
-        </is>
-      </c>
-      <c r="I115" s="4"/>
+      <c r="F114" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G114" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSK-09</t>
+        </is>
+      </c>
+      <c r="H114" s="8"/>
+      <c r="I114" s="8"/>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">J. 공통·기반   (10건 · P0 8 · P1 0)</t>
+        </is>
+      </c>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="3"/>
+      <c r="F115" s="3"/>
+      <c r="G115" s="3"/>
+      <c r="H115" s="3"/>
+      <c r="I115" s="3"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SYS-09</t>
+          <t xml:space="preserve">SYS-01</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
@@ -4802,12 +4842,12 @@
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">에러 로그 누락 수정</t>
+          <t xml:space="preserve">Alembic 마이그레이션</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">확장</t>
+          <t xml:space="preserve">신규</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -4817,222 +4857,234 @@
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">미정</t>
         </is>
       </c>
       <c r="G116" s="4"/>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">404·409·413 이 서버 로그에 남는다</t>
+          <t xml:space="preserve">create_all() 의존을 제거한다. 컬럼 추가가 데이터 유실 없이 반영된다</t>
         </is>
       </c>
       <c r="I116" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">미니 ISS-046. 첫날 수정</t>
+          <t xml:space="preserve">P0 착수 전 완료</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SYS-10</t>
-        </is>
-      </c>
-      <c r="B117" s="8" t="inlineStr">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SYS-02</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">J. 공통·기반</t>
         </is>
       </c>
-      <c r="C117" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">로컬 sLLM 옵션</t>
-        </is>
-      </c>
-      <c r="D117" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E117" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="F117" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세현</t>
-        </is>
-      </c>
-      <c r="G117" s="8"/>
-      <c r="H117" s="8"/>
-      <c r="I117" s="8"/>
-    </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">K. 산출물   (11건 · P0 0 · P1 9)</t>
-        </is>
-      </c>
-      <c r="B118" s="3"/>
-      <c r="C118" s="3"/>
-      <c r="D118" s="3"/>
-      <c r="E118" s="3"/>
-      <c r="F118" s="3"/>
-      <c r="G118" s="3"/>
-      <c r="H118" s="3"/>
-      <c r="I118" s="3"/>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Celery + Redis</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">재정</t>
+        </is>
+      </c>
+      <c r="G117" s="4"/>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">워커가 죽어도 작업이 큐에 남고 재시작 시 이어진다</t>
+        </is>
+      </c>
+      <c r="I117" s="4"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SYS-03</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">J. 공통·기반</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에러코드 체계</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">확장</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미정</t>
+        </is>
+      </c>
+      <c r="G118" s="4"/>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기존 11종에 인증·권한·프로젝트 코드를 추가. 응답 형식이 일관된다</t>
+        </is>
+      </c>
+      <c r="I118" s="4"/>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DLV-01</t>
+          <t xml:space="preserve">SYS-04</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">K. 산출물</t>
+          <t xml:space="preserve">J. 공통·기반</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">산출물 페이지 (사이드바 메뉴)</t>
+          <t xml:space="preserve">request_id 로깅</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규</t>
+          <t xml:space="preserve">기존</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
-        </is>
-      </c>
-      <c r="G119" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRJ-01</t>
-        </is>
-      </c>
+          <t xml:space="preserve">미정</t>
+        </is>
+      </c>
+      <c r="G119" s="4"/>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">사이드바에 '산출물' 메뉴가 있고 개수 배지가 붙는다</t>
-        </is>
-      </c>
-      <c r="I119" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대시보드와 분리한다 — 이력 성격</t>
-        </is>
-      </c>
+          <t xml:space="preserve">요청 단위로 로그 추적 가능</t>
+        </is>
+      </c>
+      <c r="I119" s="4"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DLV-02</t>
+          <t xml:space="preserve">SYS-05</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">K. 산출물</t>
+          <t xml:space="preserve">J. 공통·기반</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">기간 선택</t>
+          <t xml:space="preserve">Fake AI Client</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규</t>
+          <t xml:space="preserve">기존</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
-        </is>
-      </c>
-      <c r="G120" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DLV-01</t>
-        </is>
-      </c>
+          <t xml:space="preserve">미정</t>
+        </is>
+      </c>
+      <c r="G120" s="4"/>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">이번 주·지난 주·이번 달·직접 지정. 기간이 필요 없는 종류는 선택이 흐려진다</t>
-        </is>
-      </c>
-      <c r="I120" s="4"/>
+          <t xml:space="preserve">API 키 없이 전체 흐름이 동작한다</t>
+        </is>
+      </c>
+      <c r="I120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">병렬 작업의 전제</t>
+        </is>
+      </c>
     </row>
     <row r="121">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DLV-03</t>
-        </is>
-      </c>
-      <c r="B121" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">K. 산출물</t>
-        </is>
-      </c>
-      <c r="C121" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생성 대상 미리보기</t>
-        </is>
-      </c>
-      <c r="D121" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E121" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">보현</t>
-        </is>
-      </c>
-      <c r="G121" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DLV-02</t>
-        </is>
-      </c>
-      <c r="H121" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">선택한 기간에 잡히는 문서·완료 태스크·결정·기한·금액 건수가 LLM 호출 전에 보인다. 승인 대기 건수도 함께</t>
-        </is>
-      </c>
-      <c r="I121" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">빈 보고서 방지 + 비용 절약 + 승인 유도</t>
+      <c r="A121" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SYS-06</t>
+        </is>
+      </c>
+      <c r="B121" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">J. 공통·기반</t>
+        </is>
+      </c>
+      <c r="C121" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API 호출 쿼터</t>
+        </is>
+      </c>
+      <c r="D121" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E121" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F121" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미정</t>
+        </is>
+      </c>
+      <c r="G121" s="8"/>
+      <c r="H121" s="8"/>
+      <c r="I121" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로젝트별 월 한도</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DLV-04</t>
+          <t xml:space="preserve">SYS-07</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">K. 산출물</t>
+          <t xml:space="preserve">J. 공통·기반</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">주간 보고서 생성</t>
+          <t xml:space="preserve">N+1 방지</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
@@ -5042,44 +5094,40 @@
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
-        </is>
-      </c>
-      <c r="G122" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DLV-03</t>
-        </is>
-      </c>
+          <t xml:space="preserve">미정</t>
+        </is>
+      </c>
+      <c r="G122" s="4"/>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">개요·문서 목록·태스크·결정·기한·금액 변동이 한 파일로 나온다. LLM 호출은 개요 한 단락에만 1회</t>
+          <t xml:space="preserve">목록 조회 쿼리 수가 문서 수와 무관하게 일정하다. selectinload 사용</t>
         </is>
       </c>
       <c r="I122" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">tasks.completed_at 필수. 저장된 요약을 재요약한다</t>
+          <t xml:space="preserve">미니 2+2N 해소</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DLV-05</t>
+          <t xml:space="preserve">SYS-08</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">K. 산출물</t>
+          <t xml:space="preserve">J. 공통·기반</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">결정사항 대장 생성</t>
+          <t xml:space="preserve">FK 인덱스</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
@@ -5089,91 +5137,83 @@
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
+          <t xml:space="preserve">미정</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANL-14</t>
+          <t xml:space="preserve">SYS-01</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">결정 내용·결정일·출처 문서·상태(확정/미결/뒤집힘)가 표로 나온다</t>
-        </is>
-      </c>
-      <c r="I123" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미니 프로젝트 결정사항 29건을 대신한다</t>
-        </is>
-      </c>
+          <t xml:space="preserve">모든 FK 에 명시적 인덱스. PostgreSQL 은 자동 생성하지 않는다</t>
+        </is>
+      </c>
+      <c r="I123" s="4"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DLV-06</t>
+          <t xml:space="preserve">SYS-09</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">K. 산출물</t>
+          <t xml:space="preserve">J. 공통·기반</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">다음 회의 안건 생성</t>
+          <t xml:space="preserve">에러 로그 누락 수정</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규</t>
+          <t xml:space="preserve">확장</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
-        </is>
-      </c>
-      <c r="G124" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANL-14</t>
-        </is>
-      </c>
+          <t xml:space="preserve">미정</t>
+        </is>
+      </c>
+      <c r="G124" s="4"/>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">decisions.status=PENDING 인 항목만 모아 안건으로 만든다</t>
+          <t xml:space="preserve">404·409·413 이 서버 로그에 남는다</t>
         </is>
       </c>
       <c r="I124" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DLV-05 의 부산물. 거의 공짜</t>
+          <t xml:space="preserve">미니 ISS-046. 첫날 수정</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DLV-07</t>
+          <t xml:space="preserve">SYS-10</t>
         </is>
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">K. 산출물</t>
+          <t xml:space="preserve">J. 공통·기반</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">프로젝트 현황 한 장</t>
+          <t xml:space="preserve">로컬 sLLM 옵션</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
@@ -5183,77 +5223,37 @@
       </c>
       <c r="E125" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
-        </is>
-      </c>
-      <c r="G125" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANL-15</t>
-        </is>
-      </c>
-      <c r="H125" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일정·태스크·결정·금액 현재 상태를 한 페이지로</t>
-        </is>
-      </c>
+          <t xml:space="preserve">미정</t>
+        </is>
+      </c>
+      <c r="G125" s="8"/>
+      <c r="H125" s="8"/>
       <c r="I125" s="8"/>
     </row>
-    <row r="126">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DLV-08</t>
-        </is>
-      </c>
-      <c r="B126" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">K. 산출물</t>
-        </is>
-      </c>
-      <c r="C126" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">형식 선택</t>
-        </is>
-      </c>
-      <c r="D126" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E126" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F126" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">보현</t>
-        </is>
-      </c>
-      <c r="G126" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DLV-01</t>
-        </is>
-      </c>
-      <c r="H126" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">XLSX·HTML·MD. 기본값이 없다. 고르지 않으면 생성 버튼이 비활성</t>
-        </is>
-      </c>
-      <c r="I126" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_md2html.py·_build_wbs.py 재사용</t>
-        </is>
-      </c>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K. 산출물   (11건 · P0 0 · P1 9)</t>
+        </is>
+      </c>
+      <c r="B126" s="3"/>
+      <c r="C126" s="3"/>
+      <c r="D126" s="3"/>
+      <c r="E126" s="3"/>
+      <c r="F126" s="3"/>
+      <c r="G126" s="3"/>
+      <c r="H126" s="3"/>
+      <c r="I126" s="3"/>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DLV-09</t>
+          <t xml:space="preserve">DLV-01</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">생성 이력 · 다운로드</t>
+          <t xml:space="preserve">산출물 페이지 (사이드바 메뉴)</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
@@ -5283,112 +5283,1051 @@
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DLV-04</t>
+          <t xml:space="preserve">PRJ-01</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">만든 산출물이 목록으로 남고 다시 내려받을 수 있다</t>
+          <t xml:space="preserve">사이드바에 '산출물' 메뉴가 있고 개수 배지가 붙는다</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">deliverables 테이블</t>
+          <t xml:space="preserve">대시보드와 분리한다 — 이력 성격</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">DLV-02</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K. 산출물</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기간 선택</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-01</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이번 주·지난 주·이번 달·직접 지정. 기간이 필요 없는 종류는 선택이 흐려진다</t>
+        </is>
+      </c>
+      <c r="I128" s="4"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-03</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K. 산출물</t>
+        </is>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성 대상 미리보기</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-02</t>
+        </is>
+      </c>
+      <c r="H129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">선택한 기간에 잡히는 문서·완료 태스크·결정·기한·금액 건수가 LLM 호출 전에 보인다. 승인 대기 건수도 함께</t>
+        </is>
+      </c>
+      <c r="I129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">빈 보고서 방지 + 비용 절약 + 승인 유도</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-04</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K. 산출물</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주간 보고서 생성</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-03</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개요·문서 목록·태스크·결정·기한·금액 변동이 한 파일로 나온다. LLM 호출은 개요 한 단락에만 1회</t>
+        </is>
+      </c>
+      <c r="I130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tasks.completed_at 필수. 저장된 요약을 재요약한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-05</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K. 산출물</t>
+        </is>
+      </c>
+      <c r="C131" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정사항 대장 생성</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-14</t>
+        </is>
+      </c>
+      <c r="H131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정 내용·결정일·출처 문서·상태(확정/미결/뒤집힘)가 표로 나온다</t>
+        </is>
+      </c>
+      <c r="I131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미니 프로젝트 결정사항 29건을 대신한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-06</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K. 산출물</t>
+        </is>
+      </c>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다음 회의 안건 생성</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-14</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decisions.status=PENDING 인 항목만 모아 안건으로 만든다</t>
+        </is>
+      </c>
+      <c r="I132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-05 의 부산물. 거의 공짜</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-07</t>
+        </is>
+      </c>
+      <c r="B133" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K. 산출물</t>
+        </is>
+      </c>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로젝트 현황 한 장</t>
+        </is>
+      </c>
+      <c r="D133" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E133" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F133" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G133" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANL-15</t>
+        </is>
+      </c>
+      <c r="H133" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">일정·태스크·결정·금액 현재 상태를 한 페이지로</t>
+        </is>
+      </c>
+      <c r="I133" s="8"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-08</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K. 산출물</t>
+        </is>
+      </c>
+      <c r="C134" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">형식 선택</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-01</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">XLSX·HTML·MD. 기본값이 없다. 고르지 않으면 생성 버튼이 비활성</t>
+        </is>
+      </c>
+      <c r="I134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_md2html.py·_build_wbs.py 재사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-09</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K. 산출물</t>
+        </is>
+      </c>
+      <c r="C135" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성 이력 · 다운로드</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DLV-04</t>
+        </is>
+      </c>
+      <c r="H135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">만든 산출물이 목록으로 남고 다시 내려받을 수 있다</t>
+        </is>
+      </c>
+      <c r="I135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deliverables 테이블</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">DLV-10</t>
         </is>
       </c>
-      <c r="B128" s="4" t="inlineStr">
+      <c r="B136" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">K. 산출물</t>
         </is>
       </c>
-      <c r="C128" s="9" t="inlineStr">
+      <c r="C136" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">갱신 필요 판정</t>
         </is>
       </c>
-      <c r="D128" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E128" s="5" t="inlineStr">
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="F128" s="5" t="inlineStr">
+      <c r="F136" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">보현</t>
         </is>
       </c>
-      <c r="G128" s="4" t="inlineStr">
+      <c r="G136" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DLV-09</t>
         </is>
       </c>
-      <c r="H128" s="4" t="inlineStr">
+      <c r="H136" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">생성 후 문서가 추가되면 '문서 N건이 나중에 추가됨' 과 다시 만들기가 표시된다</t>
         </is>
       </c>
-      <c r="I128" s="4" t="inlineStr">
+      <c r="I136" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">source_counts_json 스냅샷 비교</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="10" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">DLV-11</t>
         </is>
       </c>
-      <c r="B129" s="8" t="inlineStr">
+      <c r="B137" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">K. 산출물</t>
         </is>
       </c>
-      <c r="C129" s="8" t="inlineStr">
+      <c r="C137" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">인수인계 문서 생성</t>
         </is>
       </c>
-      <c r="D129" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규</t>
-        </is>
-      </c>
-      <c r="E129" s="10" t="inlineStr">
+      <c r="D137" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E137" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">P3</t>
         </is>
       </c>
-      <c r="F129" s="10" t="inlineStr">
+      <c r="F137" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">보현</t>
         </is>
       </c>
-      <c r="G129" s="8" t="inlineStr">
+      <c r="G137" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">DLV-07</t>
         </is>
       </c>
-      <c r="H129" s="8"/>
-      <c r="I129" s="8" t="inlineStr">
+      <c r="H137" s="8"/>
+      <c r="I137" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">프로젝트 종료 시 전체 누적</t>
         </is>
       </c>
     </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L. 검색·근거   (12건 · P0 0 · P1 7)</t>
+        </is>
+      </c>
+      <c r="B138" s="3"/>
+      <c r="C138" s="3"/>
+      <c r="D138" s="3"/>
+      <c r="E138" s="3"/>
+      <c r="F138" s="3"/>
+      <c r="G138" s="3"/>
+      <c r="H138" s="3"/>
+      <c r="I138" s="3"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAG-01</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L. 검색·근거</t>
+        </is>
+      </c>
+      <c r="C139" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">텍스트 정규화 · 청킹</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REV-17</t>
+        </is>
+      </c>
+      <c r="H139" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ocr_elements 의 element_type 으로 단락을 묶고 토큰 수 기준으로 자른다. 표는 행 단위로 유지된다</t>
+        </is>
+      </c>
+      <c r="I139" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">재정님 단락 분리를 입력으로 쓴다</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAG-02</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L. 검색·근거</t>
+        </is>
+      </c>
+      <c r="C140" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">임베딩 생성 · 저장</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAG-01</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">청크마다 벡터가 저장되고 어느 모델·차원으로 만든 것인지 기록된다</t>
+        </is>
+      </c>
+      <c r="I140" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">document_chunks. 모델 교체 시 재생성 판단 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAG-03</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L. 검색·근거</t>
+        </is>
+      </c>
+      <c r="C141" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">벡터 인덱스 구축 (pgvector)</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAG-02</t>
+        </is>
+      </c>
+      <c r="H141" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">확장 설치와 인덱스 생성이 마이그레이션으로 반영된다</t>
+        </is>
+      </c>
+      <c r="I141" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리비전 0009. 차원은 임베딩 모델 확정 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAG-04</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L. 검색·근거</t>
+        </is>
+      </c>
+      <c r="C142" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의미 검색</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAG-03</t>
+        </is>
+      </c>
+      <c r="H142" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">글자가 하나도 겹치지 않는 질의로 관련 문서가 나온다. 다른 프로젝트 문서는 나오지 않는다</t>
+        </is>
+      </c>
+      <c r="I142" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRJ-08 스코프 강제</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAG-05</t>
+        </is>
+      </c>
+      <c r="B143" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L. 검색·근거</t>
+        </is>
+      </c>
+      <c r="C143" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하이브리드 검색 (키워드 + 벡터)</t>
+        </is>
+      </c>
+      <c r="D143" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E143" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F143" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G143" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAG-04</t>
+        </is>
+      </c>
+      <c r="H143" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고유명사·코드번호 검색에서 벡터 단독보다 정확하다</t>
+        </is>
+      </c>
+      <c r="I143" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIS-06 FTS 와 결합</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAG-06</t>
+        </is>
+      </c>
+      <c r="B144" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L. 검색·근거</t>
+        </is>
+      </c>
+      <c r="C144" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검색 결과 재순위</t>
+        </is>
+      </c>
+      <c r="D144" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E144" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="F144" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G144" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAG-05</t>
+        </is>
+      </c>
+      <c r="H144" s="8"/>
+      <c r="I144" s="8"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAG-07</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L. 검색·근거</t>
+        </is>
+      </c>
+      <c r="C145" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프롬프트 컨텍스트 조립</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAG-04</t>
+        </is>
+      </c>
+      <c r="H145" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">토큰 예산 안에서 청크를 골라 넣는다. 45000자 문서에서도 컨텍스트 초과가 나지 않는다</t>
+        </is>
+      </c>
+      <c r="I145" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">긴 문서 요약에도 쓰인다</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAG-08</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L. 검색·근거</t>
+        </is>
+      </c>
+      <c r="C146" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">근거 스니펫 연결</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAG-04</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검색·응답 결과마다 출처 문서와 원문 인용이 함께 나온다</t>
+        </is>
+      </c>
+      <c r="I146" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMT-17 · TSK-04 와 같은 패턴</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAG-09</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L. 검색·근거</t>
+        </is>
+      </c>
+      <c r="C147" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검수 확정 시 재임베딩</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REV-07</t>
+        </is>
+      </c>
+      <c r="H147" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 을 고치면 해당 문서의 청크가 다시 임베딩된다. 낡은 벡터로 검색되지 않는다</t>
+        </is>
+      </c>
+      <c r="I147" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">놓치기 쉽다. 검수 전파 사슬의 끝</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAG-10</t>
+        </is>
+      </c>
+      <c r="B148" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L. 검색·근거</t>
+        </is>
+      </c>
+      <c r="C148" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검색 품질 측정</t>
+        </is>
+      </c>
+      <c r="D148" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E148" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F148" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G148" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAG-04</t>
+        </is>
+      </c>
+      <c r="H148" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">질의 목록에 대한 적중 여부가 수치로 나온다</t>
+        </is>
+      </c>
+      <c r="I148" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">청킹 기준 변경의 판단 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAG-11</t>
+        </is>
+      </c>
+      <c r="B149" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L. 검색·근거</t>
+        </is>
+      </c>
+      <c r="C149" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">질의응답 챗봇</t>
+        </is>
+      </c>
+      <c r="D149" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E149" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="F149" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G149" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAG-07</t>
+        </is>
+      </c>
+      <c r="H149" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업로드 문서에 대해 질문하면 근거와 함께 답한다</t>
+        </is>
+      </c>
+      <c r="I149" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">후순위 합의. 검색이 먼저</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAG-12</t>
+        </is>
+      </c>
+      <c r="B150" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L. 검색·근거</t>
+        </is>
+      </c>
+      <c r="C150" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유사 사업 단가 선례 검색</t>
+        </is>
+      </c>
+      <c r="D150" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규</t>
+        </is>
+      </c>
+      <c r="E150" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F150" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+      <c r="G150" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAG-04</t>
+        </is>
+      </c>
+      <c r="H150" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">과거 사업 문서에서 같은 항목의 단가를 찾아 출처와 함께 보여준다</t>
+        </is>
+      </c>
+      <c r="I150" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비용추계의 근거. 도메인을 좁힌 이유</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I129"/>
+  <autoFilter ref="A2:I150"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5481,7 +6420,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
     </row>
@@ -5508,7 +6447,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
     </row>
@@ -5600,13 +6539,13 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C10" s="5">
         <v>4</v>
       </c>
       <c r="D10" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E10" s="5">
         <v>2</v>
@@ -5616,7 +6555,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
+          <t xml:space="preserve">세현</t>
         </is>
       </c>
     </row>
@@ -5627,16 +6566,16 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C11" s="5">
         <v>0</v>
       </c>
       <c r="D11" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E11" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F11" s="5">
         <v>0</v>
@@ -5670,7 +6609,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">미정</t>
         </is>
       </c>
     </row>
@@ -5697,7 +6636,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">공통</t>
+          <t xml:space="preserve">보현</t>
         </is>
       </c>
     </row>
@@ -5724,7 +6663,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세현</t>
+          <t xml:space="preserve">미정</t>
         </is>
       </c>
     </row>
@@ -5755,61 +6694,75 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L. 검색·근거 (RAG)</t>
+        </is>
+      </c>
+      <c r="B16" s="5">
+        <v>12</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>7</v>
+      </c>
+      <c r="E16" s="5">
+        <v>3</v>
+      </c>
+      <c r="F16" s="5">
+        <v>2</v>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보현</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">합계</t>
         </is>
       </c>
-      <c r="B16" s="3">
-        <v>116</v>
-      </c>
-      <c r="C16" s="3">
+      <c r="B17" s="3">
+        <v>136</v>
+      </c>
+      <c r="C17" s="3">
         <v>35</v>
       </c>
-      <c r="D16" s="3">
-        <v>45</v>
-      </c>
-      <c r="E16" s="3">
-        <v>25</v>
-      </c>
-      <c r="F16" s="3">
-        <v>11</v>
-      </c>
-      <c r="G16" s="3"/>
-    </row>
-    <row r="17"/>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="D17" s="3">
+        <v>58</v>
+      </c>
+      <c r="E17" s="3">
+        <v>30</v>
+      </c>
+      <c r="F17" s="3">
+        <v>13</v>
+      </c>
+      <c r="G17" s="3"/>
+    </row>
+    <row r="18"/>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">우선순위 정의</t>
         </is>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P0</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MVP 필수. 없으면 '팀 도구' 가 성립하지 않는다</t>
-        </is>
-      </c>
-      <c r="C19" s="4"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">차별화 핵심. 발표 데모의 중심</t>
+          <t xml:space="preserve">MVP 필수. 없으면 '팀 도구' 가 성립하지 않는다</t>
         </is>
       </c>
       <c r="C20" s="4"/>
@@ -5817,12 +6770,12 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">확장. 없어도 데모가 성립한다</t>
+          <t xml:space="preserve">차별화 핵심. 발표 데모의 중심</t>
         </is>
       </c>
       <c r="C21" s="4"/>
@@ -5830,48 +6783,48 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">확장. 없어도 데모가 성립한다</t>
+        </is>
+      </c>
+      <c r="C22" s="4"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">P3</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">향후. 발표에서 '향후 개선사항' 으로 배치한다</t>
         </is>
       </c>
-      <c r="C22" s="4"/>
-    </row>
-    <row r="23"/>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="C23" s="4"/>
+    </row>
+    <row r="24"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">묶음 — 같은 골격을 쓰므로 함께 만들면 두 번째부터 싸다</t>
         </is>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제안 골격</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANL-03 ANL-14 ANL-15 AMT-01 TSK-03~TSK-08 — 제안 카드·승인·태스크 등록 UI 를 공유한다. 분석기만 갈아 끼운다</t>
-        </is>
-      </c>
-      <c r="C25" s="4"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">산출물 골격</t>
+          <t xml:space="preserve">제안 골격</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DLV-01~DLV-10 — 기간 필터·파일 생성·이력이 하나로 묶인다. 종류만 늘린다</t>
+          <t xml:space="preserve">ANL-03 ANL-14 ANL-15 AMT-01 TSK-03~TSK-08 — 제안 카드·승인·태스크 등록 UI 를 공유한다. 분석기만 갈아 끼운다</t>
         </is>
       </c>
       <c r="C26" s="4"/>
@@ -5879,12 +6832,12 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">검수 골격</t>
+          <t xml:space="preserve">산출물 골격</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">REV-01~REV-07 REV-16~REV-18 — 박스 표시와 텍스트 수정이 하나로 묶인다</t>
+          <t xml:space="preserve">DLV-01~DLV-10 — 기간 필터·파일 생성·이력이 하나로 묶인다. 종류만 늘린다</t>
         </is>
       </c>
       <c r="C27" s="4"/>
@@ -5892,15 +6845,28 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">검수 골격</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REV-01~REV-07 REV-16~REV-18 — 박스 표시와 텍스트 수정이 하나로 묶인다</t>
+        </is>
+      </c>
+      <c r="C28" s="4"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">스코프</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">AUTH-* PRJ-* — 인증 없이 스코프가 성립하지 않는다</t>
         </is>
       </c>
-      <c r="C28" s="4"/>
+      <c r="C29" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/산출물/기능명세서.xlsx
+++ b/산출물/기능명세서.xlsx
@@ -3451,7 +3451,7 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보현</t>
+          <t xml:space="preserve">세현</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">미정</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">미정</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">미정</t>
+          <t xml:space="preserve">보현</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">미정</t>
+          <t xml:space="preserve">보현</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">미정</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">미정</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">미정</t>
+          <t xml:space="preserve">보현</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">미정</t>
+          <t xml:space="preserve">보현</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미정</t>
+          <t xml:space="preserve">보현</t>
         </is>
       </c>
       <c r="G104" s="8" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미정</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">미정</t>
+          <t xml:space="preserve">보현</t>
         </is>
       </c>
       <c r="G116" s="4"/>
@@ -4939,7 +4939,7 @@
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">미정</t>
+          <t xml:space="preserve">보현</t>
         </is>
       </c>
       <c r="G118" s="4"/>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">미정</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G119" s="4"/>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">미정</t>
+          <t xml:space="preserve">세현</t>
         </is>
       </c>
       <c r="G120" s="4"/>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미정</t>
+          <t xml:space="preserve">세현</t>
         </is>
       </c>
       <c r="G121" s="8"/>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">미정</t>
+          <t xml:space="preserve">보현</t>
         </is>
       </c>
       <c r="G122" s="4"/>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">미정</t>
+          <t xml:space="preserve">보현</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">미정</t>
+          <t xml:space="preserve">재정</t>
         </is>
       </c>
       <c r="G124" s="4"/>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미정</t>
+          <t xml:space="preserve">세현</t>
         </is>
       </c>
       <c r="G125" s="8"/>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">미정</t>
+          <t xml:space="preserve">공통</t>
         </is>
       </c>
     </row>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">미정</t>
+          <t xml:space="preserve">공통</t>
         </is>
       </c>
     </row>
